--- a/training_logs/equal_weighted_vs_drl_performance.xlsx
+++ b/training_logs/equal_weighted_vs_drl_performance.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +454,7 @@
         <v>100000</v>
       </c>
       <c r="C2" t="n">
-        <v>99899.99999994978</v>
+        <v>99900.00000488281</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +465,7 @@
         <v>100366.765202491</v>
       </c>
       <c r="C3" t="n">
-        <v>99832.76409921245</v>
+        <v>100272.6081365636</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>99725.02474376233</v>
       </c>
       <c r="C4" t="n">
-        <v>99371.17896515223</v>
+        <v>99678.04833674509</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         <v>100984.6018335325</v>
       </c>
       <c r="C5" t="n">
-        <v>100253.0657632559</v>
+        <v>100870.7602469377</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v>101259.7197599508</v>
       </c>
       <c r="C6" t="n">
-        <v>100672.0796573949</v>
+        <v>101117.2253086061</v>
       </c>
     </row>
     <row r="7">
@@ -509,7 +509,7 @@
         <v>101400.487592961</v>
       </c>
       <c r="C7" t="n">
-        <v>100662.9637260728</v>
+        <v>101149.0662482712</v>
       </c>
     </row>
     <row r="8">
@@ -520,7 +520,7 @@
         <v>102189.7233589838</v>
       </c>
       <c r="C8" t="n">
-        <v>101233.4882712789</v>
+        <v>101875.3370469777</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>103162.8625939997</v>
       </c>
       <c r="C9" t="n">
-        <v>101945.7995448983</v>
+        <v>102782.1071098629</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
         <v>103554.0285600798</v>
       </c>
       <c r="C10" t="n">
-        <v>102414.9829265104</v>
+        <v>103097.4158584359</v>
       </c>
     </row>
     <row r="11">
@@ -553,7 +553,7 @@
         <v>103534.8223620636</v>
       </c>
       <c r="C11" t="n">
-        <v>102395.2607168036</v>
+        <v>103075.0962467452</v>
       </c>
     </row>
     <row r="12">
@@ -564,7 +564,7 @@
         <v>103370.2814419678</v>
       </c>
       <c r="C12" t="n">
-        <v>102277.2000972979</v>
+        <v>103084.799246317</v>
       </c>
     </row>
     <row r="13">
@@ -575,7 +575,7 @@
         <v>103568.9713647209</v>
       </c>
       <c r="C13" t="n">
-        <v>102897.6191315261</v>
+        <v>103311.3711894933</v>
       </c>
     </row>
     <row r="14">
@@ -586,7 +586,7 @@
         <v>103790.4009600863</v>
       </c>
       <c r="C14" t="n">
-        <v>102858.0711061948</v>
+        <v>103403.9742733206</v>
       </c>
     </row>
     <row r="15">
@@ -597,7 +597,7 @@
         <v>104033.8593958758</v>
       </c>
       <c r="C15" t="n">
-        <v>102907.6097067231</v>
+        <v>103556.6868782256</v>
       </c>
     </row>
     <row r="16">
@@ -608,7 +608,7 @@
         <v>104115.9414547752</v>
       </c>
       <c r="C16" t="n">
-        <v>102970.7145489824</v>
+        <v>103682.8079277499</v>
       </c>
     </row>
     <row r="17">
@@ -619,7 +619,7 @@
         <v>104213.3684299711</v>
       </c>
       <c r="C17" t="n">
-        <v>103057.7453122275</v>
+        <v>103768.9725670582</v>
       </c>
     </row>
     <row r="18">
@@ -630,7 +630,7 @@
         <v>104208.7077567283</v>
       </c>
       <c r="C18" t="n">
-        <v>102895.2386707788</v>
+        <v>103717.5755622622</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +641,7 @@
         <v>104038.1338096818</v>
       </c>
       <c r="C19" t="n">
-        <v>102545.9207044568</v>
+        <v>103527.4856255333</v>
       </c>
     </row>
     <row r="20">
@@ -652,7 +652,7 @@
         <v>103249.2637177391</v>
       </c>
       <c r="C20" t="n">
-        <v>102080.3513162388</v>
+        <v>102817.9406625637</v>
       </c>
     </row>
     <row r="21">
@@ -663,7 +663,7 @@
         <v>104204.2530303209</v>
       </c>
       <c r="C21" t="n">
-        <v>102725.7503044005</v>
+        <v>103608.3280956045</v>
       </c>
     </row>
     <row r="22">
@@ -674,7 +674,7 @@
         <v>104830.0526282011</v>
       </c>
       <c r="C22" t="n">
-        <v>102737.2086273138</v>
+        <v>104223.9627748564</v>
       </c>
     </row>
     <row r="23">
@@ -685,7 +685,7 @@
         <v>104780.912395874</v>
       </c>
       <c r="C23" t="n">
-        <v>102038.9890484958</v>
+        <v>104076.1879885756</v>
       </c>
     </row>
     <row r="24">
@@ -696,7 +696,7 @@
         <v>103400.0567247366</v>
       </c>
       <c r="C24" t="n">
-        <v>100529.4168949032</v>
+        <v>102727.7132395121</v>
       </c>
     </row>
     <row r="25">
@@ -707,7 +707,7 @@
         <v>102857.1934302142</v>
       </c>
       <c r="C25" t="n">
-        <v>100497.4037868334</v>
+        <v>102240.463957454</v>
       </c>
     </row>
     <row r="26">
@@ -718,7 +718,7 @@
         <v>103317.0554880452</v>
       </c>
       <c r="C26" t="n">
-        <v>100962.4280480305</v>
+        <v>102620.1608025271</v>
       </c>
     </row>
     <row r="27">
@@ -729,7 +729,7 @@
         <v>103141.9669609163</v>
       </c>
       <c r="C27" t="n">
-        <v>101125.8642340754</v>
+        <v>102553.1396737392</v>
       </c>
     </row>
     <row r="28">
@@ -740,7 +740,7 @@
         <v>102432.1943809383</v>
       </c>
       <c r="C28" t="n">
-        <v>100634.5045400693</v>
+        <v>101935.726446155</v>
       </c>
     </row>
     <row r="29">
@@ -751,7 +751,7 @@
         <v>102532.7872915324</v>
       </c>
       <c r="C29" t="n">
-        <v>100933.8901548542</v>
+        <v>101975.734013752</v>
       </c>
     </row>
     <row r="30">
@@ -762,7 +762,7 @@
         <v>102730.5868952166</v>
       </c>
       <c r="C30" t="n">
-        <v>100794.8732809915</v>
+        <v>102100.9667715644</v>
       </c>
     </row>
     <row r="31">
@@ -773,7 +773,7 @@
         <v>102742.0458778953</v>
       </c>
       <c r="C31" t="n">
-        <v>100807.6607567809</v>
+        <v>102095.4151176291</v>
       </c>
     </row>
     <row r="32">
@@ -784,7 +784,7 @@
         <v>102497.0783248554</v>
       </c>
       <c r="C32" t="n">
-        <v>100357.7010706569</v>
+        <v>101794.9663927918</v>
       </c>
     </row>
     <row r="33">
@@ -795,7 +795,7 @@
         <v>102088.7474192719</v>
       </c>
       <c r="C33" t="n">
-        <v>100079.5734978981</v>
+        <v>101436.3039139016</v>
       </c>
     </row>
     <row r="34">
@@ -806,7 +806,7 @@
         <v>102109.1318557381</v>
       </c>
       <c r="C34" t="n">
-        <v>99978.96514488498</v>
+        <v>101470.3130164848</v>
       </c>
     </row>
     <row r="35">
@@ -817,7 +817,7 @@
         <v>101120.0001799352</v>
       </c>
       <c r="C35" t="n">
-        <v>99501.52320264679</v>
+        <v>100619.8821457514</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>100967.2855440063</v>
       </c>
       <c r="C36" t="n">
-        <v>99266.52837862051</v>
+        <v>100509.9793866755</v>
       </c>
     </row>
     <row r="37">
@@ -839,7 +839,7 @@
         <v>101544.0031685542</v>
       </c>
       <c r="C37" t="n">
-        <v>99772.78465177656</v>
+        <v>101070.4690231883</v>
       </c>
     </row>
     <row r="38">
@@ -850,7 +850,7 @@
         <v>100992.4239781086</v>
       </c>
       <c r="C38" t="n">
-        <v>99319.83407334007</v>
+        <v>100553.9954758515</v>
       </c>
     </row>
     <row r="39">
@@ -861,7 +861,7 @@
         <v>101249.4749301542</v>
       </c>
       <c r="C39" t="n">
-        <v>99473.72479812898</v>
+        <v>100806.5084103528</v>
       </c>
     </row>
     <row r="40">
@@ -872,7 +872,7 @@
         <v>101307.7098345115</v>
       </c>
       <c r="C40" t="n">
-        <v>99555.45912741411</v>
+        <v>100842.7312789787</v>
       </c>
     </row>
     <row r="41">
@@ -883,7 +883,7 @@
         <v>101503.6157984669</v>
       </c>
       <c r="C41" t="n">
-        <v>99874.9830919643</v>
+        <v>100929.725802987</v>
       </c>
     </row>
     <row r="42">
@@ -894,7 +894,7 @@
         <v>101386.3296409311</v>
       </c>
       <c r="C42" t="n">
-        <v>99799.26407485007</v>
+        <v>100794.6625752081</v>
       </c>
     </row>
     <row r="43">
@@ -905,7 +905,7 @@
         <v>102464.7819120218</v>
       </c>
       <c r="C43" t="n">
-        <v>100737.2965468281</v>
+        <v>101793.8278005675</v>
       </c>
     </row>
     <row r="44">
@@ -916,7 +916,7 @@
         <v>101922.6376228305</v>
       </c>
       <c r="C44" t="n">
-        <v>100184.7694606724</v>
+        <v>101345.9138876405</v>
       </c>
     </row>
     <row r="45">
@@ -927,7 +927,7 @@
         <v>100982.6843850927</v>
       </c>
       <c r="C45" t="n">
-        <v>99347.09247173204</v>
+        <v>100551.1962213338</v>
       </c>
     </row>
     <row r="46">
@@ -938,7 +938,7 @@
         <v>100802.001399449</v>
       </c>
       <c r="C46" t="n">
-        <v>99206.57789467872</v>
+        <v>100367.9873173235</v>
       </c>
     </row>
     <row r="47">
@@ -949,7 +949,7 @@
         <v>100332.7438539253</v>
       </c>
       <c r="C47" t="n">
-        <v>98316.77051268697</v>
+        <v>100159.5430635472</v>
       </c>
     </row>
     <row r="48">
@@ -960,7 +960,7 @@
         <v>100724.0553490039</v>
       </c>
       <c r="C48" t="n">
-        <v>98191.60726014942</v>
+        <v>100792.2630375072</v>
       </c>
     </row>
     <row r="49">
@@ -971,7 +971,7 @@
         <v>100859.6612963422</v>
       </c>
       <c r="C49" t="n">
-        <v>97888.49148078887</v>
+        <v>101087.5931089922</v>
       </c>
     </row>
     <row r="50">
@@ -982,7 +982,7 @@
         <v>100698.7347459305</v>
       </c>
       <c r="C50" t="n">
-        <v>97831.51792137991</v>
+        <v>100811.6727261686</v>
       </c>
     </row>
     <row r="51">
@@ -993,7 +993,7 @@
         <v>100431.3988906494</v>
       </c>
       <c r="C51" t="n">
-        <v>97125.5187016928</v>
+        <v>100754.9138756419</v>
       </c>
     </row>
     <row r="52">
@@ -1004,7 +1004,7 @@
         <v>100588.9043657718</v>
       </c>
       <c r="C52" t="n">
-        <v>97236.32473030029</v>
+        <v>100982.3400367628</v>
       </c>
     </row>
     <row r="53">
@@ -1015,7 +1015,7 @@
         <v>100650.4409136158</v>
       </c>
       <c r="C53" t="n">
-        <v>96655.9558602304</v>
+        <v>100765.9146010436</v>
       </c>
     </row>
     <row r="54">
@@ -1026,7 +1026,7 @@
         <v>100857.7103482798</v>
       </c>
       <c r="C54" t="n">
-        <v>96859.2366660152</v>
+        <v>101055.2163397219</v>
       </c>
     </row>
     <row r="55">
@@ -1037,7 +1037,7 @@
         <v>100950.3277658408</v>
       </c>
       <c r="C55" t="n">
-        <v>97405.68988618426</v>
+        <v>101334.2651122505</v>
       </c>
     </row>
     <row r="56">
@@ -1048,7 +1048,7 @@
         <v>101112.5907936927</v>
       </c>
       <c r="C56" t="n">
-        <v>97139.93273554118</v>
+        <v>101232.6650713692</v>
       </c>
     </row>
     <row r="57">
@@ -1059,7 +1059,7 @@
         <v>101333.2979040626</v>
       </c>
       <c r="C57" t="n">
-        <v>97193.55098348345</v>
+        <v>101451.1461526409</v>
       </c>
     </row>
     <row r="58">
@@ -1070,7 +1070,7 @@
         <v>101297.7852827849</v>
       </c>
       <c r="C58" t="n">
-        <v>97326.62629216049</v>
+        <v>101381.4711666915</v>
       </c>
     </row>
     <row r="59">
@@ -1081,7 +1081,7 @@
         <v>101364.5573484064</v>
       </c>
       <c r="C59" t="n">
-        <v>97241.95926247454</v>
+        <v>101339.7344942114</v>
       </c>
     </row>
     <row r="60">
@@ -1092,7 +1092,7 @@
         <v>101473.8725280778</v>
       </c>
       <c r="C60" t="n">
-        <v>97080.62492914447</v>
+        <v>101356.6647027686</v>
       </c>
     </row>
     <row r="61">
@@ -1103,7 +1103,7 @@
         <v>101572.5103067871</v>
       </c>
       <c r="C61" t="n">
-        <v>97504.93471640172</v>
+        <v>101677.7317759235</v>
       </c>
     </row>
     <row r="62">
@@ -1114,7 +1114,7 @@
         <v>101970.7756826298</v>
       </c>
       <c r="C62" t="n">
-        <v>97676.25709547773</v>
+        <v>102012.1672496161</v>
       </c>
     </row>
     <row r="63">
@@ -1125,7 +1125,7 @@
         <v>102538.6753049413</v>
       </c>
       <c r="C63" t="n">
-        <v>98415.91936172797</v>
+        <v>102627.3636886143</v>
       </c>
     </row>
     <row r="64">
@@ -1136,7 +1136,7 @@
         <v>103080.4722413839</v>
       </c>
       <c r="C64" t="n">
-        <v>98620.33126082795</v>
+        <v>102939.1599146547</v>
       </c>
     </row>
     <row r="65">
@@ -1147,7 +1147,7 @@
         <v>103192.5860925997</v>
       </c>
       <c r="C65" t="n">
-        <v>98318.08277766514</v>
+        <v>102873.1079752514</v>
       </c>
     </row>
     <row r="66">
@@ -1158,7 +1158,7 @@
         <v>103094.3067627364</v>
       </c>
       <c r="C66" t="n">
-        <v>98105.33639035844</v>
+        <v>102655.5578916125</v>
       </c>
     </row>
     <row r="67">
@@ -1169,7 +1169,7 @@
         <v>102917.8186806314</v>
       </c>
       <c r="C67" t="n">
-        <v>98109.54311376398</v>
+        <v>102514.1333712839</v>
       </c>
     </row>
     <row r="68">
@@ -1180,7 +1180,7 @@
         <v>102755.703917413</v>
       </c>
       <c r="C68" t="n">
-        <v>98074.47700176491</v>
+        <v>102362.7356248914</v>
       </c>
     </row>
     <row r="69">
@@ -1191,7 +1191,7 @@
         <v>103121.7442742259</v>
       </c>
       <c r="C69" t="n">
-        <v>98309.31582355736</v>
+        <v>102678.8360855029</v>
       </c>
     </row>
     <row r="70">
@@ -1202,7 +1202,7 @@
         <v>103286.3821776417</v>
       </c>
       <c r="C70" t="n">
-        <v>98226.95741797819</v>
+        <v>102717.2341056826</v>
       </c>
     </row>
     <row r="71">
@@ -1213,7 +1213,7 @@
         <v>103775.4189530556</v>
       </c>
       <c r="C71" t="n">
-        <v>98579.32544434992</v>
+        <v>103280.5146198561</v>
       </c>
     </row>
     <row r="72">
@@ -1224,7 +1224,7 @@
         <v>103193.1777065319</v>
       </c>
       <c r="C72" t="n">
-        <v>98181.1986749739</v>
+        <v>102571.0351499407</v>
       </c>
     </row>
     <row r="73">
@@ -1235,7 +1235,7 @@
         <v>103061.3653261223</v>
       </c>
       <c r="C73" t="n">
-        <v>98208.65243629219</v>
+        <v>102332.250933565</v>
       </c>
     </row>
     <row r="74">
@@ -1246,7 +1246,7 @@
         <v>103117.4943461576</v>
       </c>
       <c r="C74" t="n">
-        <v>98138.35570996626</v>
+        <v>102395.8338051516</v>
       </c>
     </row>
     <row r="75">
@@ -1257,7 +1257,7 @@
         <v>102714.3167072958</v>
       </c>
       <c r="C75" t="n">
-        <v>98022.08702353179</v>
+        <v>102036.1100259365</v>
       </c>
     </row>
     <row r="76">
@@ -1268,7 +1268,7 @@
         <v>102614.9260822958</v>
       </c>
       <c r="C76" t="n">
-        <v>97985.54180520961</v>
+        <v>101996.7966718293</v>
       </c>
     </row>
     <row r="77">
@@ -1279,7 +1279,7 @@
         <v>102396.4996998745</v>
       </c>
       <c r="C77" t="n">
-        <v>97979.29510248476</v>
+        <v>101852.1930349183</v>
       </c>
     </row>
     <row r="78">
@@ -1290,7 +1290,7 @@
         <v>102685.7068429033</v>
       </c>
       <c r="C78" t="n">
-        <v>98127.16830010558</v>
+        <v>102141.8417670888</v>
       </c>
     </row>
     <row r="79">
@@ -1301,7 +1301,7 @@
         <v>102338.6494779153</v>
       </c>
       <c r="C79" t="n">
-        <v>97832.48718933464</v>
+        <v>102011.6722451461</v>
       </c>
     </row>
     <row r="80">
@@ -1312,7 +1312,7 @@
         <v>101725.1858021165</v>
       </c>
       <c r="C80" t="n">
-        <v>97447.30300209486</v>
+        <v>101633.9106876727</v>
       </c>
     </row>
     <row r="81">
@@ -1323,7 +1323,7 @@
         <v>101900.5153346092</v>
       </c>
       <c r="C81" t="n">
-        <v>97675.67991785945</v>
+        <v>101714.1965646477</v>
       </c>
     </row>
     <row r="82">
@@ -1334,7 +1334,7 @@
         <v>102458.1238796405</v>
       </c>
       <c r="C82" t="n">
-        <v>98253.56584870887</v>
+        <v>102228.7807878863</v>
       </c>
     </row>
     <row r="83">
@@ -1345,7 +1345,7 @@
         <v>101899.9603486121</v>
       </c>
       <c r="C83" t="n">
-        <v>97770.13660263964</v>
+        <v>101657.3900674433</v>
       </c>
     </row>
     <row r="84">
@@ -1356,7 +1356,7 @@
         <v>101775.5582543451</v>
       </c>
       <c r="C84" t="n">
-        <v>97609.09862718974</v>
+        <v>101881.5228336145</v>
       </c>
     </row>
     <row r="85">
@@ -1367,7 +1367,7 @@
         <v>101919.4994637473</v>
       </c>
       <c r="C85" t="n">
-        <v>97882.43006598043</v>
+        <v>102177.1732904882</v>
       </c>
     </row>
     <row r="86">
@@ -1378,7 +1378,7 @@
         <v>101825.4136873196</v>
       </c>
       <c r="C86" t="n">
-        <v>97417.27568744338</v>
+        <v>101930.9010497012</v>
       </c>
     </row>
     <row r="87">
@@ -1389,7 +1389,7 @@
         <v>102262.4674250493</v>
       </c>
       <c r="C87" t="n">
-        <v>98611.40892861852</v>
+        <v>102077.7395707202</v>
       </c>
     </row>
     <row r="88">
@@ -1400,7 +1400,7 @@
         <v>102174.6753351467</v>
       </c>
       <c r="C88" t="n">
-        <v>98577.57922189633</v>
+        <v>101915.9547086633</v>
       </c>
     </row>
     <row r="89">
@@ -1411,7 +1411,7 @@
         <v>102275.9775354507</v>
       </c>
       <c r="C89" t="n">
-        <v>98567.1584287739</v>
+        <v>101990.7557957014</v>
       </c>
     </row>
     <row r="90">
@@ -1422,7 +1422,7 @@
         <v>102490.7766058342</v>
       </c>
       <c r="C90" t="n">
-        <v>98760.86989524981</v>
+        <v>102265.3981094527</v>
       </c>
     </row>
     <row r="91">
@@ -1433,7 +1433,7 @@
         <v>102042.4825370251</v>
       </c>
       <c r="C91" t="n">
-        <v>98224.94240982192</v>
+        <v>102043.278831975</v>
       </c>
     </row>
     <row r="92">
@@ -1444,7 +1444,7 @@
         <v>101654.3138107341</v>
       </c>
       <c r="C92" t="n">
-        <v>97826.76286091746</v>
+        <v>101755.6943225032</v>
       </c>
     </row>
     <row r="93">
@@ -1455,7 +1455,7 @@
         <v>101960.4353856593</v>
       </c>
       <c r="C93" t="n">
-        <v>98303.49320284826</v>
+        <v>101852.2979140814</v>
       </c>
     </row>
     <row r="94">
@@ -1466,7 +1466,7 @@
         <v>101205.5309192226</v>
       </c>
       <c r="C94" t="n">
-        <v>97581.51169509046</v>
+        <v>101294.800622578</v>
       </c>
     </row>
     <row r="95">
@@ -1477,7 +1477,7 @@
         <v>101675.4279726291</v>
       </c>
       <c r="C95" t="n">
-        <v>98418.03268851679</v>
+        <v>101592.1253837706</v>
       </c>
     </row>
     <row r="96">
@@ -1488,7 +1488,7 @@
         <v>101267.2427007199</v>
       </c>
       <c r="C96" t="n">
-        <v>98251.56819922767</v>
+        <v>101229.69801932</v>
       </c>
     </row>
     <row r="97">
@@ -1499,7 +1499,7 @@
         <v>101269.0495859171</v>
       </c>
       <c r="C97" t="n">
-        <v>98064.69822062101</v>
+        <v>101188.1818066927</v>
       </c>
     </row>
     <row r="98">
@@ -1510,7 +1510,7 @@
         <v>101441.7743239818</v>
       </c>
       <c r="C98" t="n">
-        <v>98385.4706911977</v>
+        <v>101290.411590312</v>
       </c>
     </row>
     <row r="99">
@@ -1521,7 +1521,7 @@
         <v>101479.1724089735</v>
       </c>
       <c r="C99" t="n">
-        <v>98397.27381034076</v>
+        <v>101345.7241508045</v>
       </c>
     </row>
     <row r="100">
@@ -1532,7 +1532,7 @@
         <v>101086.0281030006</v>
       </c>
       <c r="C100" t="n">
-        <v>98053.9998879903</v>
+        <v>101048.844086611</v>
       </c>
     </row>
     <row r="101">
@@ -1543,7 +1543,7 @@
         <v>100434.8823309657</v>
       </c>
       <c r="C101" t="n">
-        <v>97395.95253228571</v>
+        <v>100550.1866682941</v>
       </c>
     </row>
     <row r="102">
@@ -1554,7 +1554,7 @@
         <v>101039.2457444458</v>
       </c>
       <c r="C102" t="n">
-        <v>98093.86878253377</v>
+        <v>101006.4397259815</v>
       </c>
     </row>
     <row r="103">
@@ -1565,7 +1565,7 @@
         <v>100959.5194886502</v>
       </c>
       <c r="C103" t="n">
-        <v>97598.55173257175</v>
+        <v>101051.7234717326</v>
       </c>
     </row>
     <row r="104">
@@ -1576,7 +1576,7 @@
         <v>100683.7790555473</v>
       </c>
       <c r="C104" t="n">
-        <v>97174.10679359442</v>
+        <v>100901.9815768683</v>
       </c>
     </row>
     <row r="105">
@@ -1587,7 +1587,7 @@
         <v>101424.6690244455</v>
       </c>
       <c r="C105" t="n">
-        <v>97906.03382199426</v>
+        <v>101489.9321567335</v>
       </c>
     </row>
     <row r="106">
@@ -1598,7 +1598,7 @@
         <v>101855.7898457808</v>
       </c>
       <c r="C106" t="n">
-        <v>98970.21964195312</v>
+        <v>101663.2686904504</v>
       </c>
     </row>
     <row r="107">
@@ -1609,7 +1609,7 @@
         <v>101743.4363222266</v>
       </c>
       <c r="C107" t="n">
-        <v>98518.32851249883</v>
+        <v>101625.8634310734</v>
       </c>
     </row>
     <row r="108">
@@ -1620,7 +1620,7 @@
         <v>102296.4920809578</v>
       </c>
       <c r="C108" t="n">
-        <v>99231.20634674135</v>
+        <v>101958.8328085276</v>
       </c>
     </row>
     <row r="109">
@@ -1631,7 +1631,7 @@
         <v>102285.3391635212</v>
       </c>
       <c r="C109" t="n">
-        <v>99510.42782582167</v>
+        <v>101792.3013632989</v>
       </c>
     </row>
     <row r="110">
@@ -1642,7 +1642,7 @@
         <v>102668.2240112273</v>
       </c>
       <c r="C110" t="n">
-        <v>99795.17300457742</v>
+        <v>102167.7961280652</v>
       </c>
     </row>
     <row r="111">
@@ -1653,7 +1653,7 @@
         <v>102322.3670863944</v>
       </c>
       <c r="C111" t="n">
-        <v>99368.93751118706</v>
+        <v>101919.3052791954</v>
       </c>
     </row>
     <row r="112">
@@ -1664,7 +1664,7 @@
         <v>102298.7633006813</v>
       </c>
       <c r="C112" t="n">
-        <v>99120.44435473067</v>
+        <v>101961.3974063718</v>
       </c>
     </row>
     <row r="113">
@@ -1675,7 +1675,7 @@
         <v>102484.3649921477</v>
       </c>
       <c r="C113" t="n">
-        <v>99563.02615132072</v>
+        <v>102004.6338008908</v>
       </c>
     </row>
     <row r="114">
@@ -1686,7 +1686,7 @@
         <v>102384.9281421327</v>
       </c>
       <c r="C114" t="n">
-        <v>99304.22472762423</v>
+        <v>102000.7472770426</v>
       </c>
     </row>
     <row r="115">
@@ -1697,7 +1697,7 @@
         <v>103194.7394156986</v>
       </c>
       <c r="C115" t="n">
-        <v>100175.9787522373</v>
+        <v>102674.5398234252</v>
       </c>
     </row>
     <row r="116">
@@ -1708,7 +1708,7 @@
         <v>103119.3311345601</v>
       </c>
       <c r="C116" t="n">
-        <v>100402.0747217897</v>
+        <v>102606.239636732</v>
       </c>
     </row>
     <row r="117">
@@ -1719,7 +1719,7 @@
         <v>102743.70077512</v>
       </c>
       <c r="C117" t="n">
-        <v>99948.29968844917</v>
+        <v>102405.3662429543</v>
       </c>
     </row>
     <row r="118">
@@ -1730,7 +1730,7 @@
         <v>103031.9673984942</v>
       </c>
       <c r="C118" t="n">
-        <v>100327.7961163306</v>
+        <v>102706.3527524967</v>
       </c>
     </row>
     <row r="119">
@@ -1741,7 +1741,7 @@
         <v>102279.5571406354</v>
       </c>
       <c r="C119" t="n">
-        <v>99491.02008930236</v>
+        <v>102124.1166782102</v>
       </c>
     </row>
     <row r="120">
@@ -1752,7 +1752,7 @@
         <v>101957.7392153848</v>
       </c>
       <c r="C120" t="n">
-        <v>99359.16565694146</v>
+        <v>101994.3872036118</v>
       </c>
     </row>
     <row r="121">
@@ -1763,7 +1763,7 @@
         <v>102104.3013763285</v>
       </c>
       <c r="C121" t="n">
-        <v>99469.25298744249</v>
+        <v>102133.7391740847</v>
       </c>
     </row>
     <row r="122">
@@ -1774,7 +1774,7 @@
         <v>101990.9781104033</v>
       </c>
       <c r="C122" t="n">
-        <v>98910.69717032806</v>
+        <v>102006.2858236603</v>
       </c>
     </row>
     <row r="123">
@@ -1785,7 +1785,7 @@
         <v>102056.8855291238</v>
       </c>
       <c r="C123" t="n">
-        <v>98858.40814482818</v>
+        <v>102094.9734379589</v>
       </c>
     </row>
     <row r="124">
@@ -1796,7 +1796,7 @@
         <v>102032.8895855806</v>
       </c>
       <c r="C124" t="n">
-        <v>98659.66873297049</v>
+        <v>101885.5136295214</v>
       </c>
     </row>
     <row r="125">
@@ -1807,7 +1807,7 @@
         <v>102557.3782980271</v>
       </c>
       <c r="C125" t="n">
-        <v>99128.8193318284</v>
+        <v>102339.6448340687</v>
       </c>
     </row>
     <row r="126">
@@ -1818,7 +1818,7 @@
         <v>102597.5167280268</v>
       </c>
       <c r="C126" t="n">
-        <v>99084.42921778283</v>
+        <v>102337.8761858842</v>
       </c>
     </row>
     <row r="127">
@@ -1829,7 +1829,7 @@
         <v>102296.5960314504</v>
       </c>
       <c r="C127" t="n">
-        <v>99050.3515026838</v>
+        <v>102060.5351550879</v>
       </c>
     </row>
     <row r="128">
@@ -1840,7 +1840,7 @@
         <v>101574.41261241</v>
       </c>
       <c r="C128" t="n">
-        <v>98778.12524928426</v>
+        <v>101393.4410188736</v>
       </c>
     </row>
     <row r="129">
@@ -1851,7 +1851,7 @@
         <v>101992.8456943909</v>
       </c>
       <c r="C129" t="n">
-        <v>99155.4303320192</v>
+        <v>101615.6112463685</v>
       </c>
     </row>
     <row r="130">
@@ -1862,7 +1862,7 @@
         <v>102480.8273335088</v>
       </c>
       <c r="C130" t="n">
-        <v>99319.88794116004</v>
+        <v>101983.0812847343</v>
       </c>
     </row>
     <row r="131">
@@ -1873,7 +1873,7 @@
         <v>103063.5230487792</v>
       </c>
       <c r="C131" t="n">
-        <v>99757.54046617786</v>
+        <v>102427.9195556585</v>
       </c>
     </row>
     <row r="132">
@@ -1884,7 +1884,7 @@
         <v>103961.479779258</v>
       </c>
       <c r="C132" t="n">
-        <v>100483.6656900229</v>
+        <v>103209.5384973243</v>
       </c>
     </row>
     <row r="133">
@@ -1895,7 +1895,7 @@
         <v>104653.9771128797</v>
       </c>
       <c r="C133" t="n">
-        <v>101024.6794931687</v>
+        <v>103846.6299561232</v>
       </c>
     </row>
     <row r="134">
@@ -1906,7 +1906,7 @@
         <v>104123.2059926232</v>
       </c>
       <c r="C134" t="n">
-        <v>100655.4201330317</v>
+        <v>103402.5711902965</v>
       </c>
     </row>
     <row r="135">
@@ -1917,7 +1917,7 @@
         <v>104248.9897435121</v>
       </c>
       <c r="C135" t="n">
-        <v>100496.6114387602</v>
+        <v>103481.9860945509</v>
       </c>
     </row>
     <row r="136">
@@ -1928,7 +1928,7 @@
         <v>105006.6634208414</v>
       </c>
       <c r="C136" t="n">
-        <v>101149.9777351657</v>
+        <v>103999.8323086273</v>
       </c>
     </row>
     <row r="137">
@@ -1939,7 +1939,7 @@
         <v>105174.5910161658</v>
       </c>
       <c r="C137" t="n">
-        <v>101356.7526168397</v>
+        <v>104106.7348087129</v>
       </c>
     </row>
     <row r="138">
@@ -1950,7 +1950,7 @@
         <v>104787.6627635816</v>
       </c>
       <c r="C138" t="n">
-        <v>101196.8799503078</v>
+        <v>103764.5295083476</v>
       </c>
     </row>
     <row r="139">
@@ -1961,7 +1961,7 @@
         <v>104830.711675299</v>
       </c>
       <c r="C139" t="n">
-        <v>101278.2437007844</v>
+        <v>103844.6453168734</v>
       </c>
     </row>
     <row r="140">
@@ -1972,7 +1972,7 @@
         <v>105106.6305818843</v>
       </c>
       <c r="C140" t="n">
-        <v>101591.7788874997</v>
+        <v>104013.3419449509</v>
       </c>
     </row>
     <row r="141">
@@ -1983,7 +1983,7 @@
         <v>105226.1466075905</v>
       </c>
       <c r="C141" t="n">
-        <v>101802.5819078558</v>
+        <v>104063.4380197892</v>
       </c>
     </row>
     <row r="142">
@@ -1994,7 +1994,7 @@
         <v>105494.3110898646</v>
       </c>
       <c r="C142" t="n">
-        <v>101883.2044917214</v>
+        <v>104290.9653194172</v>
       </c>
     </row>
     <row r="143">
@@ -2005,7 +2005,7 @@
         <v>104620.572472101</v>
       </c>
       <c r="C143" t="n">
-        <v>101212.4941100028</v>
+        <v>103560.2013778556</v>
       </c>
     </row>
     <row r="144">
@@ -2016,7 +2016,7 @@
         <v>105381.8656455052</v>
       </c>
       <c r="C144" t="n">
-        <v>101663.1558542487</v>
+        <v>104180.8985619983</v>
       </c>
     </row>
     <row r="145">
@@ -2027,7 +2027,7 @@
         <v>105777.1061433819</v>
       </c>
       <c r="C145" t="n">
-        <v>101885.4347539125</v>
+        <v>104436.4591563466</v>
       </c>
     </row>
     <row r="146">
@@ -2038,7 +2038,7 @@
         <v>105136.5693781154</v>
       </c>
       <c r="C146" t="n">
-        <v>101334.4402403245</v>
+        <v>103851.5936321732</v>
       </c>
     </row>
     <row r="147">
@@ -2049,7 +2049,7 @@
         <v>104360.219249222</v>
       </c>
       <c r="C147" t="n">
-        <v>100753.9167947022</v>
+        <v>103285.6551387999</v>
       </c>
     </row>
     <row r="148">
@@ -2060,7 +2060,7 @@
         <v>104216.0504576754</v>
       </c>
       <c r="C148" t="n">
-        <v>100839.3955600375</v>
+        <v>103028.5582344904</v>
       </c>
     </row>
     <row r="149">
@@ -2071,7 +2071,7 @@
         <v>104640.6340144794</v>
       </c>
       <c r="C149" t="n">
-        <v>101184.9439848655</v>
+        <v>103565.7414247609</v>
       </c>
     </row>
     <row r="150">
@@ -2082,7 +2082,7 @@
         <v>104537.8454845595</v>
       </c>
       <c r="C150" t="n">
-        <v>101098.9183364077</v>
+        <v>103444.6635387198</v>
       </c>
     </row>
     <row r="151">
@@ -2093,7 +2093,7 @@
         <v>104396.5381899885</v>
       </c>
       <c r="C151" t="n">
-        <v>101004.1653208916</v>
+        <v>103457.5863008618</v>
       </c>
     </row>
     <row r="152">
@@ -2104,7 +2104,7 @@
         <v>104327.9905307561</v>
       </c>
       <c r="C152" t="n">
-        <v>101070.0771645412</v>
+        <v>103473.1453158651</v>
       </c>
     </row>
     <row r="153">
@@ -2115,7 +2115,7 @@
         <v>103984.4539328624</v>
       </c>
       <c r="C153" t="n">
-        <v>100779.281171502</v>
+        <v>103151.0582953123</v>
       </c>
     </row>
     <row r="154">
@@ -2126,7 +2126,7 @@
         <v>103891.5980361335</v>
       </c>
       <c r="C154" t="n">
-        <v>100661.3419163047</v>
+        <v>103017.7932211861</v>
       </c>
     </row>
     <row r="155">
@@ -2137,7 +2137,7 @@
         <v>103566.6504809801</v>
       </c>
       <c r="C155" t="n">
-        <v>100434.2190415128</v>
+        <v>102720.926062144</v>
       </c>
     </row>
     <row r="156">
@@ -2148,7 +2148,7 @@
         <v>102896.4119781467</v>
       </c>
       <c r="C156" t="n">
-        <v>99966.03917325904</v>
+        <v>102217.148042884</v>
       </c>
     </row>
     <row r="157">
@@ -2159,7 +2159,7 @@
         <v>102427.5608111559</v>
       </c>
       <c r="C157" t="n">
-        <v>99746.48246864024</v>
+        <v>101892.0940608695</v>
       </c>
     </row>
     <row r="158">
@@ -2170,7 +2170,7 @@
         <v>102208.1721828069</v>
       </c>
       <c r="C158" t="n">
-        <v>99774.88772229236</v>
+        <v>101774.0714733121</v>
       </c>
     </row>
     <row r="159">
@@ -2181,7 +2181,7 @@
         <v>102458.3243857348</v>
       </c>
       <c r="C159" t="n">
-        <v>100000.898271213</v>
+        <v>101953.2963967819</v>
       </c>
     </row>
     <row r="160">
@@ -2192,7 +2192,7 @@
         <v>102274.3649949877</v>
       </c>
       <c r="C160" t="n">
-        <v>99696.71672017191</v>
+        <v>101726.4932316122</v>
       </c>
     </row>
     <row r="161">
@@ -2203,7 +2203,7 @@
         <v>102327.0114856159</v>
       </c>
       <c r="C161" t="n">
-        <v>99811.43410896677</v>
+        <v>101816.0222044177</v>
       </c>
     </row>
     <row r="162">
@@ -2214,7 +2214,7 @@
         <v>103151.5234098438</v>
       </c>
       <c r="C162" t="n">
-        <v>100492.9561177529</v>
+        <v>102594.8394927712</v>
       </c>
     </row>
     <row r="163">
@@ -2225,7 +2225,7 @@
         <v>102763.6618925254</v>
       </c>
       <c r="C163" t="n">
-        <v>100243.2272398348</v>
+        <v>102299.4091764208</v>
       </c>
     </row>
     <row r="164">
@@ -2236,7 +2236,7 @@
         <v>103009.1950191693</v>
       </c>
       <c r="C164" t="n">
-        <v>100388.3543854256</v>
+        <v>102468.1486087884</v>
       </c>
     </row>
     <row r="165">
@@ -2247,7 +2247,7 @@
         <v>103276.4005196133</v>
       </c>
       <c r="C165" t="n">
-        <v>100740.6033147558</v>
+        <v>102664.7715592272</v>
       </c>
     </row>
     <row r="166">
@@ -2258,7 +2258,7 @@
         <v>104044.4227670379</v>
       </c>
       <c r="C166" t="n">
-        <v>101517.0034627523</v>
+        <v>103303.8606485797</v>
       </c>
     </row>
     <row r="167">
@@ -2269,7 +2269,7 @@
         <v>104125.8200973421</v>
       </c>
       <c r="C167" t="n">
-        <v>101537.7944018886</v>
+        <v>103320.8130046943</v>
       </c>
     </row>
     <row r="168">
@@ -2280,7 +2280,7 @@
         <v>104155.3059412998</v>
       </c>
       <c r="C168" t="n">
-        <v>101524.9324297314</v>
+        <v>103375.3448553323</v>
       </c>
     </row>
     <row r="169">
@@ -2291,7 +2291,7 @@
         <v>104462.738207433</v>
       </c>
       <c r="C169" t="n">
-        <v>101654.134574051</v>
+        <v>103462.3599193942</v>
       </c>
     </row>
     <row r="170">
@@ -2302,7 +2302,7 @@
         <v>103753.6945637873</v>
       </c>
       <c r="C170" t="n">
-        <v>100668.8379919378</v>
+        <v>102915.2325108998</v>
       </c>
     </row>
     <row r="171">
@@ -2313,7 +2313,7 @@
         <v>103606.5644706041</v>
       </c>
       <c r="C171" t="n">
-        <v>100666.5845535368</v>
+        <v>102812.4482668101</v>
       </c>
     </row>
     <row r="172">
@@ -2324,7 +2324,7 @@
         <v>103573.3886435314</v>
       </c>
       <c r="C172" t="n">
-        <v>100849.561638556</v>
+        <v>102931.9433895177</v>
       </c>
     </row>
     <row r="173">
@@ -2335,7 +2335,7 @@
         <v>103594.6671396885</v>
       </c>
       <c r="C173" t="n">
-        <v>100930.1856232052</v>
+        <v>102971.6625814715</v>
       </c>
     </row>
     <row r="174">
@@ -2346,7 +2346,7 @@
         <v>103724.1749060204</v>
       </c>
       <c r="C174" t="n">
-        <v>101007.8780996047</v>
+        <v>103024.2955169049</v>
       </c>
     </row>
     <row r="175">
@@ -2357,7 +2357,7 @@
         <v>103704.9634193927</v>
       </c>
       <c r="C175" t="n">
-        <v>101136.4425727387</v>
+        <v>103039.1049899667</v>
       </c>
     </row>
     <row r="176">
@@ -2368,7 +2368,7 @@
         <v>103642.5332827387</v>
       </c>
       <c r="C176" t="n">
-        <v>101275.5579886278</v>
+        <v>103063.0199218236</v>
       </c>
     </row>
     <row r="177">
@@ -2379,7 +2379,7 @@
         <v>104031.9916069815</v>
       </c>
       <c r="C177" t="n">
-        <v>101463.9123869708</v>
+        <v>103253.7141434871</v>
       </c>
     </row>
     <row r="178">
@@ -2390,7 +2390,7 @@
         <v>103828.5889428558</v>
       </c>
       <c r="C178" t="n">
-        <v>101272.8249398111</v>
+        <v>103110.5259459191</v>
       </c>
     </row>
     <row r="179">
@@ -2401,7 +2401,7 @@
         <v>103835.6948795762</v>
       </c>
       <c r="C179" t="n">
-        <v>101307.5331595834</v>
+        <v>103168.0094873898</v>
       </c>
     </row>
     <row r="180">
@@ -2412,7 +2412,7 @@
         <v>103708.7172652635</v>
       </c>
       <c r="C180" t="n">
-        <v>101243.7760453274</v>
+        <v>103058.8170474484</v>
       </c>
     </row>
     <row r="181">
@@ -2423,7 +2423,7 @@
         <v>103367.5967510791</v>
       </c>
       <c r="C181" t="n">
-        <v>100987.0744035355</v>
+        <v>102846.479742277</v>
       </c>
     </row>
     <row r="182">
@@ -2434,7 +2434,7 @@
         <v>102647.5352056446</v>
       </c>
       <c r="C182" t="n">
-        <v>100507.4052785945</v>
+        <v>102258.9236762274</v>
       </c>
     </row>
     <row r="183">
@@ -2445,7 +2445,7 @@
         <v>102818.5568810849</v>
       </c>
       <c r="C183" t="n">
-        <v>100737.3571008834</v>
+        <v>102479.163195277</v>
       </c>
     </row>
     <row r="184">
@@ -2456,7 +2456,7 @@
         <v>102504.0549449187</v>
       </c>
       <c r="C184" t="n">
-        <v>100290.3787342415</v>
+        <v>102092.2559679651</v>
       </c>
     </row>
     <row r="185">
@@ -2467,7 +2467,7 @@
         <v>101997.8013693706</v>
       </c>
       <c r="C185" t="n">
-        <v>100072.1613274454</v>
+        <v>101726.0745138227</v>
       </c>
     </row>
     <row r="186">
@@ -2478,7 +2478,7 @@
         <v>101912.0992083891</v>
       </c>
       <c r="C186" t="n">
-        <v>100018.3449663115</v>
+        <v>101548.8894504959</v>
       </c>
     </row>
     <row r="187">
@@ -2489,7 +2489,7 @@
         <v>102049.7951326632</v>
       </c>
       <c r="C187" t="n">
-        <v>100121.4897954374</v>
+        <v>101670.2679198603</v>
       </c>
     </row>
     <row r="188">
@@ -2500,7 +2500,7 @@
         <v>101582.3794032453</v>
       </c>
       <c r="C188" t="n">
-        <v>99814.47565417817</v>
+        <v>101352.545780079</v>
       </c>
     </row>
     <row r="189">
@@ -2511,7 +2511,7 @@
         <v>100724.3691893842</v>
       </c>
       <c r="C189" t="n">
-        <v>99187.9198331229</v>
+        <v>100642.0947045012</v>
       </c>
     </row>
     <row r="190">
@@ -2522,7 +2522,7 @@
         <v>99999.77202954343</v>
       </c>
       <c r="C190" t="n">
-        <v>98604.27607125524</v>
+        <v>100009.9142189412</v>
       </c>
     </row>
     <row r="191">
@@ -2533,7 +2533,7 @@
         <v>99717.5038209421</v>
       </c>
       <c r="C191" t="n">
-        <v>98102.2867522185</v>
+        <v>99921.10625391724</v>
       </c>
     </row>
     <row r="192">
@@ -2544,7 +2544,7 @@
         <v>99618.06429270198</v>
       </c>
       <c r="C192" t="n">
-        <v>97923.60159077377</v>
+        <v>99921.60774043971</v>
       </c>
     </row>
     <row r="193">
@@ -2555,7 +2555,7 @@
         <v>99869.4682437318</v>
       </c>
       <c r="C193" t="n">
-        <v>98387.29760550456</v>
+        <v>100070.4422439594</v>
       </c>
     </row>
     <row r="194">
@@ -2566,7 +2566,7 @@
         <v>100865.2614113758</v>
       </c>
       <c r="C194" t="n">
-        <v>99616.03189975386</v>
+        <v>100774.687560523</v>
       </c>
     </row>
     <row r="195">
@@ -2577,7 +2577,7 @@
         <v>100998.414086671</v>
       </c>
       <c r="C195" t="n">
-        <v>99834.26072489619</v>
+        <v>100930.3095512763</v>
       </c>
     </row>
     <row r="196">
@@ -2588,7 +2588,7 @@
         <v>101206.5009344948</v>
       </c>
       <c r="C196" t="n">
-        <v>100031.2248238029</v>
+        <v>101323.7611899331</v>
       </c>
     </row>
     <row r="197">
@@ -2599,7 +2599,7 @@
         <v>100454.7755128057</v>
       </c>
       <c r="C197" t="n">
-        <v>99114.2470222657</v>
+        <v>100522.5443070391</v>
       </c>
     </row>
     <row r="198">
@@ -2610,7 +2610,7 @@
         <v>101427.3290828705</v>
       </c>
       <c r="C198" t="n">
-        <v>100389.2784408114</v>
+        <v>101074.1454903822</v>
       </c>
     </row>
     <row r="199">
@@ -2621,7 +2621,7 @@
         <v>101452.6883122326</v>
       </c>
       <c r="C199" t="n">
-        <v>100688.3259836303</v>
+        <v>101180.2624648814</v>
       </c>
     </row>
     <row r="200">
@@ -2632,7 +2632,7 @@
         <v>101536.8370045419</v>
       </c>
       <c r="C200" t="n">
-        <v>100925.3740745447</v>
+        <v>101251.5019083787</v>
       </c>
     </row>
     <row r="201">
@@ -2643,7 +2643,7 @@
         <v>101415.6146822657</v>
       </c>
       <c r="C201" t="n">
-        <v>100458.6985327093</v>
+        <v>101008.6629695345</v>
       </c>
     </row>
     <row r="202">
@@ -2654,7 +2654,7 @@
         <v>101363.5941449563</v>
       </c>
       <c r="C202" t="n">
-        <v>100148.1276803689</v>
+        <v>100798.4990206424</v>
       </c>
     </row>
     <row r="203">
@@ -2665,7 +2665,7 @@
         <v>101222.1114952392</v>
       </c>
       <c r="C203" t="n">
-        <v>99777.57003075321</v>
+        <v>100808.3731155471</v>
       </c>
     </row>
     <row r="204">
@@ -2676,7 +2676,7 @@
         <v>101071.9862530574</v>
       </c>
       <c r="C204" t="n">
-        <v>99554.70694505237</v>
+        <v>100758.4874743461</v>
       </c>
     </row>
     <row r="205">
@@ -2687,7 +2687,7 @@
         <v>101209.1071963411</v>
       </c>
       <c r="C205" t="n">
-        <v>99693.34281746575</v>
+        <v>101139.4417932504</v>
       </c>
     </row>
     <row r="206">
@@ -2698,7 +2698,7 @@
         <v>100894.5919414814</v>
       </c>
       <c r="C206" t="n">
-        <v>99276.12030479104</v>
+        <v>100686.3120685637</v>
       </c>
     </row>
     <row r="207">
@@ -2709,7 +2709,7 @@
         <v>101002.9266445326</v>
       </c>
       <c r="C207" t="n">
-        <v>99241.07875283726</v>
+        <v>100943.5714983359</v>
       </c>
     </row>
     <row r="208">
@@ -2720,7 +2720,7 @@
         <v>101263.714854524</v>
       </c>
       <c r="C208" t="n">
-        <v>99301.88299071285</v>
+        <v>101030.4314373164</v>
       </c>
     </row>
     <row r="209">
@@ -2731,7 +2731,7 @@
         <v>100975.9916125286</v>
       </c>
       <c r="C209" t="n">
-        <v>99099.70445074602</v>
+        <v>101037.3587999034</v>
       </c>
     </row>
     <row r="210">
@@ -2742,7 +2742,7 @@
         <v>100943.4833412591</v>
       </c>
       <c r="C210" t="n">
-        <v>99213.85445442008</v>
+        <v>101049.6276390659</v>
       </c>
     </row>
     <row r="211">
@@ -2753,7 +2753,7 @@
         <v>101386.1675336831</v>
       </c>
       <c r="C211" t="n">
-        <v>99730.78036322913</v>
+        <v>101500.7482900503</v>
       </c>
     </row>
     <row r="212">
@@ -2764,7 +2764,7 @@
         <v>102324.5814967152</v>
       </c>
       <c r="C212" t="n">
-        <v>100866.3941519243</v>
+        <v>102320.437115908</v>
       </c>
     </row>
     <row r="213">
@@ -2775,7 +2775,7 @@
         <v>103016.2695334601</v>
       </c>
       <c r="C213" t="n">
-        <v>101955.0355976744</v>
+        <v>102893.300681644</v>
       </c>
     </row>
     <row r="214">
@@ -2786,7 +2786,7 @@
         <v>102519.6618958208</v>
       </c>
       <c r="C214" t="n">
-        <v>101309.7405879975</v>
+        <v>102457.2495732306</v>
       </c>
     </row>
     <row r="215">
@@ -2797,7 +2797,7 @@
         <v>102164.0496199286</v>
       </c>
       <c r="C215" t="n">
-        <v>101438.6232045432</v>
+        <v>102372.3048310449</v>
       </c>
     </row>
     <row r="216">
@@ -2808,7 +2808,7 @@
         <v>101708.205501552</v>
       </c>
       <c r="C216" t="n">
-        <v>101297.9699315919</v>
+        <v>102203.0955325552</v>
       </c>
     </row>
     <row r="217">
@@ -2819,7 +2819,7 @@
         <v>101190.5542538255</v>
       </c>
       <c r="C217" t="n">
-        <v>100468.6114667699</v>
+        <v>101676.4026108805</v>
       </c>
     </row>
     <row r="218">
@@ -2830,7 +2830,7 @@
         <v>101371.6285138446</v>
       </c>
       <c r="C218" t="n">
-        <v>100910.0704765371</v>
+        <v>101864.9937343529</v>
       </c>
     </row>
     <row r="219">
@@ -2841,7 +2841,7 @@
         <v>101624.2171479431</v>
       </c>
       <c r="C219" t="n">
-        <v>100729.1141329385</v>
+        <v>101936.2424118782</v>
       </c>
     </row>
     <row r="220">
@@ -2852,7 +2852,7 @@
         <v>103156.2597457637</v>
       </c>
       <c r="C220" t="n">
-        <v>102517.1881191282</v>
+        <v>103264.5896670833</v>
       </c>
     </row>
     <row r="221">
@@ -2863,7 +2863,7 @@
         <v>102831.6877590846</v>
       </c>
       <c r="C221" t="n">
-        <v>102241.3831738322</v>
+        <v>102910.6612112323</v>
       </c>
     </row>
     <row r="222">
@@ -2874,7 +2874,7 @@
         <v>102598.7609143452</v>
       </c>
       <c r="C222" t="n">
-        <v>101437.0821260928</v>
+        <v>103112.1718333222</v>
       </c>
     </row>
     <row r="223">
@@ -2885,7 +2885,7 @@
         <v>103147.0253397653</v>
       </c>
       <c r="C223" t="n">
-        <v>102231.7261390431</v>
+        <v>103445.5516010292</v>
       </c>
     </row>
     <row r="224">
@@ -2896,7 +2896,7 @@
         <v>103560.3021056788</v>
       </c>
       <c r="C224" t="n">
-        <v>102860.6539463151</v>
+        <v>103761.8075744099</v>
       </c>
     </row>
     <row r="225">
@@ -2907,7 +2907,7 @@
         <v>103655.6640941408</v>
       </c>
       <c r="C225" t="n">
-        <v>102670.4778993699</v>
+        <v>103838.1562391603</v>
       </c>
     </row>
     <row r="226">
@@ -2918,7 +2918,7 @@
         <v>103647.4974415013</v>
       </c>
       <c r="C226" t="n">
-        <v>102702.7303364068</v>
+        <v>103939.5853541002</v>
       </c>
     </row>
     <row r="227">
@@ -2929,7 +2929,7 @@
         <v>103633.1320568992</v>
       </c>
       <c r="C227" t="n">
-        <v>102360.7776776119</v>
+        <v>103746.9613618332</v>
       </c>
     </row>
     <row r="228">
@@ -2940,7 +2940,7 @@
         <v>103766.4033603024</v>
       </c>
       <c r="C228" t="n">
-        <v>102462.807725357</v>
+        <v>103975.2611813</v>
       </c>
     </row>
     <row r="229">
@@ -2951,7 +2951,7 @@
         <v>104308.5569359878</v>
       </c>
       <c r="C229" t="n">
-        <v>103019.0131418485</v>
+        <v>104518.2913293393</v>
       </c>
     </row>
     <row r="230">
@@ -2962,7 +2962,7 @@
         <v>104774.7647051455</v>
       </c>
       <c r="C230" t="n">
-        <v>103543.1922793979</v>
+        <v>104984.6842838239</v>
       </c>
     </row>
     <row r="231">
@@ -2973,7 +2973,7 @@
         <v>104306.9857985338</v>
       </c>
       <c r="C231" t="n">
-        <v>102849.9202252037</v>
+        <v>104457.7291376162</v>
       </c>
     </row>
     <row r="232">
@@ -2984,7 +2984,7 @@
         <v>105471.4745656324</v>
       </c>
       <c r="C232" t="n">
-        <v>103349.3759262729</v>
+        <v>105255.9233102697</v>
       </c>
     </row>
     <row r="233">
@@ -2995,7 +2995,7 @@
         <v>104958.3055242131</v>
       </c>
       <c r="C233" t="n">
-        <v>102893.6390051652</v>
+        <v>104686.6152814274</v>
       </c>
     </row>
     <row r="234">
@@ -3006,7 +3006,7 @@
         <v>104715.7097127147</v>
       </c>
       <c r="C234" t="n">
-        <v>102984.3697740713</v>
+        <v>104801.1169254341</v>
       </c>
     </row>
     <row r="235">
@@ -3017,7 +3017,7 @@
         <v>104507.577516091</v>
       </c>
       <c r="C235" t="n">
-        <v>102587.5002241852</v>
+        <v>104699.3309522672</v>
       </c>
     </row>
     <row r="236">
@@ -3028,7 +3028,7 @@
         <v>104679.4399352014</v>
       </c>
       <c r="C236" t="n">
-        <v>102608.6592941518</v>
+        <v>104736.5053918654</v>
       </c>
     </row>
     <row r="237">
@@ -3039,7 +3039,7 @@
         <v>104496.5064573279</v>
       </c>
       <c r="C237" t="n">
-        <v>102502.1147939563</v>
+        <v>104457.1552948793</v>
       </c>
     </row>
     <row r="238">
@@ -3050,7 +3050,7 @@
         <v>104252.8945907014</v>
       </c>
       <c r="C238" t="n">
-        <v>102376.9018758429</v>
+        <v>104257.3551641709</v>
       </c>
     </row>
     <row r="239">
@@ -3061,7 +3061,7 @@
         <v>104073.8020091301</v>
       </c>
       <c r="C239" t="n">
-        <v>102132.2824615591</v>
+        <v>104166.0058505565</v>
       </c>
     </row>
     <row r="240">
@@ -3072,7 +3072,7 @@
         <v>105792.8781519082</v>
       </c>
       <c r="C240" t="n">
-        <v>103131.3340822565</v>
+        <v>105390.1149073598</v>
       </c>
     </row>
     <row r="241">
@@ -3083,7 +3083,7 @@
         <v>107013.7497106072</v>
       </c>
       <c r="C241" t="n">
-        <v>103918.665086042</v>
+        <v>106221.4846211242</v>
       </c>
     </row>
     <row r="242">
@@ -3094,7 +3094,7 @@
         <v>106661.3261034754</v>
       </c>
       <c r="C242" t="n">
-        <v>103689.5958385856</v>
+        <v>106085.1752732372</v>
       </c>
     </row>
     <row r="243">
@@ -3105,7 +3105,7 @@
         <v>106838.1780960967</v>
       </c>
       <c r="C243" t="n">
-        <v>103946.4752266881</v>
+        <v>106203.6467638919</v>
       </c>
     </row>
     <row r="244">
@@ -3116,7 +3116,7 @@
         <v>107536.3052025781</v>
       </c>
       <c r="C244" t="n">
-        <v>104373.2588167912</v>
+        <v>106524.9768886686</v>
       </c>
     </row>
     <row r="245">
@@ -3127,7 +3127,7 @@
         <v>106928.8167131868</v>
       </c>
       <c r="C245" t="n">
-        <v>104015.5219939714</v>
+        <v>106361.3329919582</v>
       </c>
     </row>
     <row r="246">
@@ -3138,7 +3138,7 @@
         <v>107455.0109345242</v>
       </c>
       <c r="C246" t="n">
-        <v>104258.5757673975</v>
+        <v>106530.4195569259</v>
       </c>
     </row>
     <row r="247">
@@ -3149,7 +3149,7 @@
         <v>107656.0010297969</v>
       </c>
       <c r="C247" t="n">
-        <v>104313.2883737949</v>
+        <v>106496.7148551836</v>
       </c>
     </row>
     <row r="248">
@@ -3160,7 +3160,7 @@
         <v>108298.5543492037</v>
       </c>
       <c r="C248" t="n">
-        <v>104799.7427153342</v>
+        <v>106861.8090106708</v>
       </c>
     </row>
     <row r="249">
@@ -3171,7 +3171,7 @@
         <v>108558.7564188225</v>
       </c>
       <c r="C249" t="n">
-        <v>104968.7381559503</v>
+        <v>107105.122829173</v>
       </c>
     </row>
     <row r="250">
@@ -3182,7 +3182,7 @@
         <v>108152.1976924704</v>
       </c>
       <c r="C250" t="n">
-        <v>104544.950401134</v>
+        <v>106782.9039874433</v>
       </c>
     </row>
     <row r="251">
@@ -3193,7 +3193,7 @@
         <v>107598.9459934505</v>
       </c>
       <c r="C251" t="n">
-        <v>104309.7468980926</v>
+        <v>106514.8350679072</v>
       </c>
     </row>
     <row r="252">
@@ -3204,7 +3204,7 @@
         <v>107051.4060973887</v>
       </c>
       <c r="C252" t="n">
-        <v>103924.3305069855</v>
+        <v>105982.3501400422</v>
       </c>
     </row>
     <row r="253">
@@ -3215,7 +3215,7 @@
         <v>106526.8292086154</v>
       </c>
       <c r="C253" t="n">
-        <v>104058.5851428761</v>
+        <v>106016.4922269793</v>
       </c>
     </row>
     <row r="254">
@@ -3226,7 +3226,7 @@
         <v>106267.9720388962</v>
       </c>
       <c r="C254" t="n">
-        <v>103838.0680967443</v>
+        <v>105713.133672686</v>
       </c>
     </row>
     <row r="255">
@@ -3237,7 +3237,7 @@
         <v>106188.7808359249</v>
       </c>
       <c r="C255" t="n">
-        <v>103895.9543256406</v>
+        <v>105635.9144637319</v>
       </c>
     </row>
     <row r="256">
@@ -3248,7 +3248,7 @@
         <v>106253.554276666</v>
       </c>
       <c r="C256" t="n">
-        <v>103434.3192206414</v>
+        <v>105474.5545067114</v>
       </c>
     </row>
     <row r="257">
@@ -3259,7 +3259,7 @@
         <v>106133.1245438951</v>
       </c>
       <c r="C257" t="n">
-        <v>103629.9728878199</v>
+        <v>105490.1500951241</v>
       </c>
     </row>
     <row r="258">
@@ -3270,7 +3270,7 @@
         <v>106092.9445337794</v>
       </c>
       <c r="C258" t="n">
-        <v>103352.6312436427</v>
+        <v>105500.9138755695</v>
       </c>
     </row>
     <row r="259">
@@ -3281,7 +3281,7 @@
         <v>106360.4791943086</v>
       </c>
       <c r="C259" t="n">
-        <v>103743.6768994933</v>
+        <v>106028.200654406</v>
       </c>
     </row>
     <row r="260">
@@ -3292,7 +3292,7 @@
         <v>106640.1368594675</v>
       </c>
       <c r="C260" t="n">
-        <v>104150.7106655051</v>
+        <v>106300.4209372407</v>
       </c>
     </row>
     <row r="261">
@@ -3303,7 +3303,7 @@
         <v>105800.6954894739</v>
       </c>
       <c r="C261" t="n">
-        <v>103494.5178917638</v>
+        <v>105626.3676780159</v>
       </c>
     </row>
     <row r="262">
@@ -3314,7 +3314,7 @@
         <v>105339.2217847847</v>
       </c>
       <c r="C262" t="n">
-        <v>103118.3970743916</v>
+        <v>105332.3354334821</v>
       </c>
     </row>
     <row r="263">
@@ -3325,7 +3325,7 @@
         <v>105698.7947251234</v>
       </c>
       <c r="C263" t="n">
-        <v>103466.2601532469</v>
+        <v>105517.7227773878</v>
       </c>
     </row>
     <row r="264">
@@ -3336,7 +3336,7 @@
         <v>105915.81933608</v>
       </c>
       <c r="C264" t="n">
-        <v>103503.0813418262</v>
+        <v>105539.4305713426</v>
       </c>
     </row>
     <row r="265">
@@ -3347,7 +3347,7 @@
         <v>106357.1002250964</v>
       </c>
       <c r="C265" t="n">
-        <v>103559.0474971136</v>
+        <v>105631.2593178331</v>
       </c>
     </row>
     <row r="266">
@@ -3358,7 +3358,7 @@
         <v>106326.5947214214</v>
       </c>
       <c r="C266" t="n">
-        <v>103741.2254853528</v>
+        <v>105562.0671441581</v>
       </c>
     </row>
     <row r="267">
@@ -3369,7 +3369,7 @@
         <v>106072.9979914816</v>
       </c>
       <c r="C267" t="n">
-        <v>103701.7143000091</v>
+        <v>105488.5732862725</v>
       </c>
     </row>
     <row r="268">
@@ -3380,7 +3380,7 @@
         <v>106643.9918194856</v>
       </c>
       <c r="C268" t="n">
-        <v>104138.2085850034</v>
+        <v>105976.9077304195</v>
       </c>
     </row>
     <row r="269">
@@ -3391,7 +3391,7 @@
         <v>106707.1676153434</v>
       </c>
       <c r="C269" t="n">
-        <v>104198.8131844134</v>
+        <v>106043.7588437655</v>
       </c>
     </row>
     <row r="270">
@@ -3402,7 +3402,7 @@
         <v>107170.9578607012</v>
       </c>
       <c r="C270" t="n">
-        <v>104268.7522871153</v>
+        <v>106186.5714556633</v>
       </c>
     </row>
     <row r="271">
@@ -3413,7 +3413,7 @@
         <v>107213.2399397128</v>
       </c>
       <c r="C271" t="n">
-        <v>104527.2452971705</v>
+        <v>106419.4170840057</v>
       </c>
     </row>
     <row r="272">
@@ -3424,7 +3424,7 @@
         <v>106599.6438708798</v>
       </c>
       <c r="C272" t="n">
-        <v>104348.1153368211</v>
+        <v>106309.9834221984</v>
       </c>
     </row>
     <row r="273">
@@ -3435,7 +3435,7 @@
         <v>107113.8645386503</v>
       </c>
       <c r="C273" t="n">
-        <v>104484.2743979441</v>
+        <v>106625.1313008567</v>
       </c>
     </row>
     <row r="274">
@@ -3446,7 +3446,7 @@
         <v>106346.9453973237</v>
       </c>
       <c r="C274" t="n">
-        <v>103700.9396388197</v>
+        <v>105882.0819594293</v>
       </c>
     </row>
     <row r="275">
@@ -3457,7 +3457,7 @@
         <v>105779.998131774</v>
       </c>
       <c r="C275" t="n">
-        <v>103453.6647036599</v>
+        <v>105453.2230181096</v>
       </c>
     </row>
     <row r="276">
@@ -3468,7 +3468,7 @@
         <v>106351.8766493362</v>
       </c>
       <c r="C276" t="n">
-        <v>103811.7312255954</v>
+        <v>105930.8392253728</v>
       </c>
     </row>
     <row r="277">
@@ -3479,7 +3479,7 @@
         <v>106320.7046064126</v>
       </c>
       <c r="C277" t="n">
-        <v>103877.6404798051</v>
+        <v>105925.4349970111</v>
       </c>
     </row>
     <row r="278">
@@ -3490,7 +3490,7 @@
         <v>106617.0044055069</v>
       </c>
       <c r="C278" t="n">
-        <v>103939.8042919948</v>
+        <v>105921.1504957145</v>
       </c>
     </row>
     <row r="279">
@@ -3501,7 +3501,7 @@
         <v>106894.1420201264</v>
       </c>
       <c r="C279" t="n">
-        <v>103890.9264979222</v>
+        <v>105918.2356039879</v>
       </c>
     </row>
     <row r="280">
@@ -3512,7 +3512,7 @@
         <v>107229.7189913738</v>
       </c>
       <c r="C280" t="n">
-        <v>103844.6502061115</v>
+        <v>105932.7065253253</v>
       </c>
     </row>
     <row r="281">
@@ -3523,7 +3523,7 @@
         <v>105692.139637293</v>
       </c>
       <c r="C281" t="n">
-        <v>103105.6921485255</v>
+        <v>105141.6167378261</v>
       </c>
     </row>
     <row r="282">
@@ -3534,7 +3534,7 @@
         <v>106162.7121559675</v>
       </c>
       <c r="C282" t="n">
-        <v>102947.6940000663</v>
+        <v>105249.0284559788</v>
       </c>
     </row>
     <row r="283">
@@ -3545,7 +3545,7 @@
         <v>107042.1446282635</v>
       </c>
       <c r="C283" t="n">
-        <v>103264.8870399817</v>
+        <v>105646.8921402949</v>
       </c>
     </row>
     <row r="284">
@@ -3556,7 +3556,7 @@
         <v>106694.4366184011</v>
       </c>
       <c r="C284" t="n">
-        <v>103336.2834286703</v>
+        <v>105472.8142537836</v>
       </c>
     </row>
     <row r="285">
@@ -3567,7 +3567,7 @@
         <v>106468.7551952308</v>
       </c>
       <c r="C285" t="n">
-        <v>103389.9749426962</v>
+        <v>105475.4185408132</v>
       </c>
     </row>
     <row r="286">
@@ -3578,7 +3578,7 @@
         <v>106382.7825518602</v>
       </c>
       <c r="C286" t="n">
-        <v>103427.8692175413</v>
+        <v>105457.9673967286</v>
       </c>
     </row>
     <row r="287">
@@ -3589,7 +3589,7 @@
         <v>106707.8876644164</v>
       </c>
       <c r="C287" t="n">
-        <v>103529.5025045401</v>
+        <v>105686.0756982778</v>
       </c>
     </row>
     <row r="288">
@@ -3600,7 +3600,7 @@
         <v>106789.203868061</v>
       </c>
       <c r="C288" t="n">
-        <v>103399.4451433898</v>
+        <v>105726.7616439623</v>
       </c>
     </row>
     <row r="289">
@@ -3611,7 +3611,7 @@
         <v>106933.7552158294</v>
       </c>
       <c r="C289" t="n">
-        <v>103528.3422496145</v>
+        <v>105742.031461271</v>
       </c>
     </row>
     <row r="290">
@@ -3622,7 +3622,7 @@
         <v>107276.1970339766</v>
       </c>
       <c r="C290" t="n">
-        <v>103666.5533592164</v>
+        <v>105817.4350714127</v>
       </c>
     </row>
     <row r="291">
@@ -3633,7 +3633,7 @@
         <v>107157.0944681827</v>
       </c>
       <c r="C291" t="n">
-        <v>103666.9531316239</v>
+        <v>105869.7973651256</v>
       </c>
     </row>
     <row r="292">
@@ -3644,7 +3644,7 @@
         <v>107467.6762935709</v>
       </c>
       <c r="C292" t="n">
-        <v>103822.1335846585</v>
+        <v>106039.697572541</v>
       </c>
     </row>
     <row r="293">
@@ -3655,7 +3655,7 @@
         <v>108291.2092593889</v>
       </c>
       <c r="C293" t="n">
-        <v>104559.608453359</v>
+        <v>106602.7926777088</v>
       </c>
     </row>
     <row r="294">
@@ -3666,7 +3666,7 @@
         <v>108571.7964624518</v>
       </c>
       <c r="C294" t="n">
-        <v>105012.3865336559</v>
+        <v>106770.4152004942</v>
       </c>
     </row>
     <row r="295">
@@ -3677,7 +3677,7 @@
         <v>108507.1608245851</v>
       </c>
       <c r="C295" t="n">
-        <v>105119.3148471196</v>
+        <v>106896.054380242</v>
       </c>
     </row>
     <row r="296">
@@ -3688,7 +3688,7 @@
         <v>109047.034321467</v>
       </c>
       <c r="C296" t="n">
-        <v>105551.2934990448</v>
+        <v>107280.3042181781</v>
       </c>
     </row>
     <row r="297">
@@ -3699,7 +3699,7 @@
         <v>109452.5883178666</v>
       </c>
       <c r="C297" t="n">
-        <v>105747.0956767943</v>
+        <v>107507.2688475274</v>
       </c>
     </row>
     <row r="298">
@@ -3710,7 +3710,7 @@
         <v>109592.8507224659</v>
       </c>
       <c r="C298" t="n">
-        <v>105721.3206199761</v>
+        <v>107576.4098134758</v>
       </c>
     </row>
     <row r="299">
@@ -3721,7 +3721,7 @@
         <v>109572.3128640984</v>
       </c>
       <c r="C299" t="n">
-        <v>105897.2932739768</v>
+        <v>107725.714328127</v>
       </c>
     </row>
     <row r="300">
@@ -3732,7 +3732,7 @@
         <v>109211.6405478385</v>
       </c>
       <c r="C300" t="n">
-        <v>105715.1925222434</v>
+        <v>107457.218545154</v>
       </c>
     </row>
     <row r="301">
@@ -3743,7 +3743,7 @@
         <v>109642.9514993633</v>
       </c>
       <c r="C301" t="n">
-        <v>106069.5491417931</v>
+        <v>107794.9269018383</v>
       </c>
     </row>
     <row r="302">
@@ -3754,7 +3754,7 @@
         <v>109064.4778914433</v>
       </c>
       <c r="C302" t="n">
-        <v>105875.0500860898</v>
+        <v>107555.0468785483</v>
       </c>
     </row>
     <row r="303">
@@ -3765,7 +3765,7 @@
         <v>109032.7442182527</v>
       </c>
       <c r="C303" t="n">
-        <v>105876.128320166</v>
+        <v>107511.2732371033</v>
       </c>
     </row>
     <row r="304">
@@ -3776,7 +3776,7 @@
         <v>109093.8291485884</v>
       </c>
       <c r="C304" t="n">
-        <v>106104.6671231005</v>
+        <v>107696.6976875967</v>
       </c>
     </row>
     <row r="305">
@@ -3787,7 +3787,7 @@
         <v>109279.4000617553</v>
       </c>
       <c r="C305" t="n">
-        <v>106288.139670056</v>
+        <v>107868.7002471749</v>
       </c>
     </row>
     <row r="306">
@@ -3798,7 +3798,7 @@
         <v>109981.1409057558</v>
       </c>
       <c r="C306" t="n">
-        <v>106399.2382135011</v>
+        <v>108085.9351986536</v>
       </c>
     </row>
     <row r="307">
@@ -3809,7 +3809,7 @@
         <v>110255.0920137341</v>
       </c>
       <c r="C307" t="n">
-        <v>106488.9054481894</v>
+        <v>108170.9536915941</v>
       </c>
     </row>
     <row r="308">
@@ -3820,7 +3820,7 @@
         <v>109822.8721852293</v>
       </c>
       <c r="C308" t="n">
-        <v>106485.1556637516</v>
+        <v>108141.1060046873</v>
       </c>
     </row>
     <row r="309">
@@ -3831,7 +3831,7 @@
         <v>110021.1957431464</v>
       </c>
       <c r="C309" t="n">
-        <v>106633.6912401239</v>
+        <v>108266.0127011753</v>
       </c>
     </row>
     <row r="310">
@@ -3842,7 +3842,7 @@
         <v>109933.017354375</v>
       </c>
       <c r="C310" t="n">
-        <v>106447.6005276605</v>
+        <v>108151.5199059712</v>
       </c>
     </row>
     <row r="311">
@@ -3853,7 +3853,7 @@
         <v>110645.8984147732</v>
       </c>
       <c r="C311" t="n">
-        <v>106642.6051514794</v>
+        <v>108399.1466491232</v>
       </c>
     </row>
     <row r="312">
@@ -3864,7 +3864,7 @@
         <v>111056.7560909284</v>
       </c>
       <c r="C312" t="n">
-        <v>106806.5918899643</v>
+        <v>108591.0969705591</v>
       </c>
     </row>
     <row r="313">
@@ -3875,7 +3875,7 @@
         <v>110950.7855746047</v>
       </c>
       <c r="C313" t="n">
-        <v>106642.0343559269</v>
+        <v>108471.5727909788</v>
       </c>
     </row>
     <row r="314">
@@ -3886,7 +3886,7 @@
         <v>111018.6888141293</v>
       </c>
       <c r="C314" t="n">
-        <v>106872.8626753487</v>
+        <v>108756.1940882579</v>
       </c>
     </row>
     <row r="315">
@@ -3897,7 +3897,7 @@
         <v>111586.7507543316</v>
       </c>
       <c r="C315" t="n">
-        <v>107278.248354478</v>
+        <v>109157.7818768069</v>
       </c>
     </row>
     <row r="316">
@@ -3908,7 +3908,7 @@
         <v>111348.9909061303</v>
       </c>
       <c r="C316" t="n">
-        <v>107408.8084244491</v>
+        <v>109234.9638334826</v>
       </c>
     </row>
     <row r="317">
@@ -3919,7 +3919,7 @@
         <v>111799.7534359393</v>
       </c>
       <c r="C317" t="n">
-        <v>107458.9867708123</v>
+        <v>109373.2956575107</v>
       </c>
     </row>
     <row r="318">
@@ -3930,7 +3930,7 @@
         <v>112026.0292356681</v>
       </c>
       <c r="C318" t="n">
-        <v>107436.6499472387</v>
+        <v>109390.992229275</v>
       </c>
     </row>
     <row r="319">
@@ -3941,7 +3941,7 @@
         <v>112316.0223209556</v>
       </c>
       <c r="C319" t="n">
-        <v>107570.0929754891</v>
+        <v>109593.746414409</v>
       </c>
     </row>
     <row r="320">
@@ -3952,7 +3952,7 @@
         <v>111169.7276687665</v>
       </c>
       <c r="C320" t="n">
-        <v>106961.136196928</v>
+        <v>108885.0273208935</v>
       </c>
     </row>
     <row r="321">
@@ -3963,7 +3963,7 @@
         <v>111635.6796431521</v>
       </c>
       <c r="C321" t="n">
-        <v>106849.8229167494</v>
+        <v>108900.4233227332</v>
       </c>
     </row>
     <row r="322">
@@ -3974,7 +3974,7 @@
         <v>111009.7489945043</v>
       </c>
       <c r="C322" t="n">
-        <v>106870.9034610014</v>
+        <v>108831.9720911443</v>
       </c>
     </row>
     <row r="323">
@@ -3985,7 +3985,7 @@
         <v>110818.339232574</v>
       </c>
       <c r="C323" t="n">
-        <v>106424.111556355</v>
+        <v>108484.3600812732</v>
       </c>
     </row>
     <row r="324">
@@ -3996,7 +3996,7 @@
         <v>110647.169814929</v>
       </c>
       <c r="C324" t="n">
-        <v>106231.3826932679</v>
+        <v>108305.9932487705</v>
       </c>
     </row>
     <row r="325">
@@ -4007,7 +4007,7 @@
         <v>110244.8306779141</v>
       </c>
       <c r="C325" t="n">
-        <v>106158.1442660704</v>
+        <v>108263.8592413569</v>
       </c>
     </row>
     <row r="326">
@@ -4018,7 +4018,7 @@
         <v>110242.7873253145</v>
       </c>
       <c r="C326" t="n">
-        <v>106066.0168447642</v>
+        <v>108193.6520072085</v>
       </c>
     </row>
     <row r="327">
@@ -4029,7 +4029,7 @@
         <v>110496.3132825708</v>
       </c>
       <c r="C327" t="n">
-        <v>106304.5289540695</v>
+        <v>108428.8363259927</v>
       </c>
     </row>
     <row r="328">
@@ -4040,7 +4040,7 @@
         <v>110282.5034370379</v>
       </c>
       <c r="C328" t="n">
-        <v>106462.2790268777</v>
+        <v>108433.8013722673</v>
       </c>
     </row>
     <row r="329">
@@ -4051,7 +4051,7 @@
         <v>110682.8254671418</v>
       </c>
       <c r="C329" t="n">
-        <v>106664.8106299796</v>
+        <v>108601.7799989172</v>
       </c>
     </row>
     <row r="330">
@@ -4062,7 +4062,7 @@
         <v>110363.4877072797</v>
       </c>
       <c r="C330" t="n">
-        <v>106375.1910863733</v>
+        <v>108307.8204462014</v>
       </c>
     </row>
     <row r="331">
@@ -4073,7 +4073,7 @@
         <v>110369.9246036221</v>
       </c>
       <c r="C331" t="n">
-        <v>106375.8452279133</v>
+        <v>108316.1824085388</v>
       </c>
     </row>
     <row r="332">
@@ -4084,7 +4084,7 @@
         <v>110757.498610441</v>
       </c>
       <c r="C332" t="n">
-        <v>106579.3161765245</v>
+        <v>108534.8746913639</v>
       </c>
     </row>
     <row r="333">
@@ -4095,7 +4095,7 @@
         <v>110998.376305312</v>
       </c>
       <c r="C333" t="n">
-        <v>106769.4527683728</v>
+        <v>108718.8721198511</v>
       </c>
     </row>
     <row r="334">
@@ -4106,7 +4106,7 @@
         <v>109714.343350058</v>
       </c>
       <c r="C334" t="n">
-        <v>106061.288535574</v>
+        <v>107956.1262632171</v>
       </c>
     </row>
     <row r="335">
@@ -4117,7 +4117,7 @@
         <v>109836.7766800227</v>
       </c>
       <c r="C335" t="n">
-        <v>105893.5491020822</v>
+        <v>107905.4149366892</v>
       </c>
     </row>
     <row r="336">
@@ -4128,7 +4128,7 @@
         <v>110408.0222259438</v>
       </c>
       <c r="C336" t="n">
-        <v>106318.8303050319</v>
+        <v>108300.093882008</v>
       </c>
     </row>
     <row r="337">
@@ -4139,7 +4139,7 @@
         <v>110847.7886507613</v>
       </c>
       <c r="C337" t="n">
-        <v>106713.9171894306</v>
+        <v>108687.3300212779</v>
       </c>
     </row>
     <row r="338">
@@ -4150,7 +4150,7 @@
         <v>111581.1245065362</v>
       </c>
       <c r="C338" t="n">
-        <v>107110.5517306483</v>
+        <v>109092.1461954331</v>
       </c>
     </row>
     <row r="339">
@@ -4161,7 +4161,7 @@
         <v>111565.1442299776</v>
       </c>
       <c r="C339" t="n">
-        <v>107163.6617436917</v>
+        <v>109126.4554828873</v>
       </c>
     </row>
     <row r="340">
@@ -4172,7 +4172,7 @@
         <v>111193.2687901816</v>
       </c>
       <c r="C340" t="n">
-        <v>106867.8027563389</v>
+        <v>108836.8012148466</v>
       </c>
     </row>
     <row r="341">
@@ -4183,7 +4183,7 @@
         <v>111905.5766401795</v>
       </c>
       <c r="C341" t="n">
-        <v>107142.3372114548</v>
+        <v>109178.7449463947</v>
       </c>
     </row>
     <row r="342">
@@ -4194,7 +4194,7 @@
         <v>111807.4215422612</v>
       </c>
       <c r="C342" t="n">
-        <v>106963.0674615355</v>
+        <v>109048.4197543249</v>
       </c>
     </row>
     <row r="343">
@@ -4205,7 +4205,7 @@
         <v>111756.3361012014</v>
       </c>
       <c r="C343" t="n">
-        <v>107189.4341297217</v>
+        <v>109184.9413978022</v>
       </c>
     </row>
     <row r="344">
@@ -4216,7 +4216,7 @@
         <v>112163.4240002988</v>
       </c>
       <c r="C344" t="n">
-        <v>107216.305070928</v>
+        <v>109279.781766597</v>
       </c>
     </row>
     <row r="345">
@@ -4227,7 +4227,7 @@
         <v>113057.3070033341</v>
       </c>
       <c r="C345" t="n">
-        <v>107767.5883311457</v>
+        <v>109891.9265836405</v>
       </c>
     </row>
     <row r="346">
@@ -4238,7 +4238,7 @@
         <v>112782.5022268386</v>
       </c>
       <c r="C346" t="n">
-        <v>107709.2115586723</v>
+        <v>109797.058956438</v>
       </c>
     </row>
     <row r="347">
@@ -4249,7 +4249,7 @@
         <v>113249.4949047575</v>
       </c>
       <c r="C347" t="n">
-        <v>107872.088945964</v>
+        <v>109996.9422449902</v>
       </c>
     </row>
     <row r="348">
@@ -4260,7 +4260,7 @@
         <v>113523.2502700758</v>
       </c>
       <c r="C348" t="n">
-        <v>108095.5057469075</v>
+        <v>110197.9223748288</v>
       </c>
     </row>
     <row r="349">
@@ -4271,7 +4271,7 @@
         <v>113451.297302804</v>
       </c>
       <c r="C349" t="n">
-        <v>108059.8875389574</v>
+        <v>110176.8302731751</v>
       </c>
     </row>
     <row r="350">
@@ -4282,7 +4282,7 @@
         <v>112551.4303897088</v>
       </c>
       <c r="C350" t="n">
-        <v>107552.9344447674</v>
+        <v>109637.3529595246</v>
       </c>
     </row>
     <row r="351">
@@ -4293,7 +4293,7 @@
         <v>111536.2021169474</v>
       </c>
       <c r="C351" t="n">
-        <v>107168.1718152784</v>
+        <v>109164.3185835617</v>
       </c>
     </row>
     <row r="352">
@@ -4304,7 +4304,7 @@
         <v>111986.2651143739</v>
       </c>
       <c r="C352" t="n">
-        <v>107488.9473534227</v>
+        <v>109457.8164753405</v>
       </c>
     </row>
     <row r="353">
@@ -4315,7 +4315,7 @@
         <v>112290.6640478217</v>
       </c>
       <c r="C353" t="n">
-        <v>107678.7633319902</v>
+        <v>109616.6818273522</v>
       </c>
     </row>
     <row r="354">
@@ -4326,7 +4326,7 @@
         <v>111486.7563839626</v>
       </c>
       <c r="C354" t="n">
-        <v>107201.3894593736</v>
+        <v>109136.3731229349</v>
       </c>
     </row>
     <row r="355">
@@ -4337,7 +4337,7 @@
         <v>111679.8120566102</v>
       </c>
       <c r="C355" t="n">
-        <v>107130.8688511993</v>
+        <v>109134.7894218981</v>
       </c>
     </row>
     <row r="356">
@@ -4348,7 +4348,7 @@
         <v>111803.5893361989</v>
       </c>
       <c r="C356" t="n">
-        <v>107242.3359469111</v>
+        <v>109242.8608527253</v>
       </c>
     </row>
     <row r="357">
@@ -4359,7 +4359,7 @@
         <v>111822.199958364</v>
       </c>
       <c r="C357" t="n">
-        <v>107142.9920599496</v>
+        <v>109248.2671448918</v>
       </c>
     </row>
     <row r="358">
@@ -4370,7 +4370,7 @@
         <v>111288.0117084328</v>
       </c>
       <c r="C358" t="n">
-        <v>107004.8543251847</v>
+        <v>109111.2304739801</v>
       </c>
     </row>
     <row r="359">
@@ -4381,7 +4381,7 @@
         <v>111997.2655563973</v>
       </c>
       <c r="C359" t="n">
-        <v>107245.1786730296</v>
+        <v>109395.2424675023</v>
       </c>
     </row>
     <row r="360">
@@ -4392,7 +4392,7 @@
         <v>112191.4861494582</v>
       </c>
       <c r="C360" t="n">
-        <v>107546.1427669351</v>
+        <v>109672.0882609162</v>
       </c>
     </row>
     <row r="361">
@@ -4403,7 +4403,7 @@
         <v>110672.400761725</v>
       </c>
       <c r="C361" t="n">
-        <v>106740.1524924312</v>
+        <v>108739.6145087133</v>
       </c>
     </row>
     <row r="362">
@@ -4414,7 +4414,7 @@
         <v>111141.1731987175</v>
       </c>
       <c r="C362" t="n">
-        <v>107086.4494433994</v>
+        <v>109063.7508120605</v>
       </c>
     </row>
     <row r="363">
@@ -4425,7 +4425,7 @@
         <v>111254.5997438103</v>
       </c>
       <c r="C363" t="n">
-        <v>107263.1235835365</v>
+        <v>109265.2433442078</v>
       </c>
     </row>
     <row r="364">
@@ -4436,7 +4436,7 @@
         <v>111830.2527761814</v>
       </c>
       <c r="C364" t="n">
-        <v>107594.3594354146</v>
+        <v>109598.572513296</v>
       </c>
     </row>
     <row r="365">
@@ -4447,7 +4447,7 @@
         <v>111629.1947804948</v>
       </c>
       <c r="C365" t="n">
-        <v>107810.9931184407</v>
+        <v>109773.6337749445</v>
       </c>
     </row>
     <row r="366">
@@ -4458,7 +4458,7 @@
         <v>111529.4488819196</v>
       </c>
       <c r="C366" t="n">
-        <v>107724.6404114778</v>
+        <v>109769.0792467805</v>
       </c>
     </row>
     <row r="367">
@@ -4469,7 +4469,7 @@
         <v>111521.7821029189</v>
       </c>
       <c r="C367" t="n">
-        <v>107638.9498363704</v>
+        <v>109648.1393200168</v>
       </c>
     </row>
     <row r="368">
@@ -4480,7 +4480,7 @@
         <v>111967.4438382073</v>
       </c>
       <c r="C368" t="n">
-        <v>108138.7089406834</v>
+        <v>110140.6855481715</v>
       </c>
     </row>
     <row r="369">
@@ -4491,7 +4491,7 @@
         <v>112082.4733776744</v>
       </c>
       <c r="C369" t="n">
-        <v>108050.5284812503</v>
+        <v>110090.4219393669</v>
       </c>
     </row>
     <row r="370">
@@ -4502,7 +4502,7 @@
         <v>111695.3023388898</v>
       </c>
       <c r="C370" t="n">
-        <v>107881.5319493642</v>
+        <v>109889.9630798652</v>
       </c>
     </row>
     <row r="371">
@@ -4513,7 +4513,7 @@
         <v>112021.2319659051</v>
       </c>
       <c r="C371" t="n">
-        <v>108132.6624412564</v>
+        <v>110128.9033041464</v>
       </c>
     </row>
     <row r="372">
@@ -4524,7 +4524,7 @@
         <v>111703.1851071564</v>
       </c>
       <c r="C372" t="n">
-        <v>107892.5461182437</v>
+        <v>109902.3744706069</v>
       </c>
     </row>
     <row r="373">
@@ -4535,7 +4535,7 @@
         <v>111342.0442658971</v>
       </c>
       <c r="C373" t="n">
-        <v>107722.3228958329</v>
+        <v>109685.9354232176</v>
       </c>
     </row>
     <row r="374">
@@ -4546,7 +4546,7 @@
         <v>111916.2775310092</v>
       </c>
       <c r="C374" t="n">
-        <v>107941.5050200137</v>
+        <v>109934.6330199919</v>
       </c>
     </row>
     <row r="375">
@@ -4557,7 +4557,7 @@
         <v>111703.4636751342</v>
       </c>
       <c r="C375" t="n">
-        <v>107496.380577017</v>
+        <v>109499.6777025665</v>
       </c>
     </row>
     <row r="376">
@@ -4568,7 +4568,7 @@
         <v>111646.2921745277</v>
       </c>
       <c r="C376" t="n">
-        <v>107600.7763898412</v>
+        <v>109563.0096252753</v>
       </c>
     </row>
     <row r="377">
@@ -4579,7 +4579,7 @@
         <v>111879.8489827495</v>
       </c>
       <c r="C377" t="n">
-        <v>107849.5063862665</v>
+        <v>109810.7394813947</v>
       </c>
     </row>
     <row r="378">
@@ -4590,7 +4590,7 @@
         <v>112456.3177779587</v>
       </c>
       <c r="C378" t="n">
-        <v>108370.3991705248</v>
+        <v>110365.2778785033</v>
       </c>
     </row>
     <row r="379">
@@ -4601,7 +4601,7 @@
         <v>112923.143172598</v>
       </c>
       <c r="C379" t="n">
-        <v>108784.0297041834</v>
+        <v>110827.707935835</v>
       </c>
     </row>
     <row r="380">
@@ -4612,7 +4612,7 @@
         <v>112562.5588619508</v>
       </c>
       <c r="C380" t="n">
-        <v>108413.6903461626</v>
+        <v>110453.8768830411</v>
       </c>
     </row>
     <row r="381">
@@ -4623,7 +4623,7 @@
         <v>112329.5694016007</v>
       </c>
       <c r="C381" t="n">
-        <v>108132.7518436948</v>
+        <v>110199.8032042322</v>
       </c>
     </row>
     <row r="382">
@@ -4634,7 +4634,7 @@
         <v>112705.6645729477</v>
       </c>
       <c r="C382" t="n">
-        <v>108284.9619040173</v>
+        <v>110368.7384613533</v>
       </c>
     </row>
     <row r="383">
@@ -4645,7 +4645,7 @@
         <v>114061.7852883252</v>
       </c>
       <c r="C383" t="n">
-        <v>108677.1341924551</v>
+        <v>110822.6580175598</v>
       </c>
     </row>
     <row r="384">
@@ -4656,7 +4656,7 @@
         <v>114315.7702129683</v>
       </c>
       <c r="C384" t="n">
-        <v>108710.5698372511</v>
+        <v>110868.8968210811</v>
       </c>
     </row>
     <row r="385">
@@ -4667,7 +4667,7 @@
         <v>114528.8492412321</v>
       </c>
       <c r="C385" t="n">
-        <v>108320.849642531</v>
+        <v>110511.707565083</v>
       </c>
     </row>
     <row r="386">
@@ -4678,7 +4678,7 @@
         <v>115800.5513350462</v>
       </c>
       <c r="C386" t="n">
-        <v>108480.0476974206</v>
+        <v>110760.6649558084</v>
       </c>
     </row>
     <row r="387">
@@ -4689,7 +4689,7 @@
         <v>115417.7677126187</v>
       </c>
       <c r="C387" t="n">
-        <v>108410.7997647405</v>
+        <v>110670.3758911396</v>
       </c>
     </row>
     <row r="388">
@@ -4700,7 +4700,7 @@
         <v>114589.0958845046</v>
       </c>
       <c r="C388" t="n">
-        <v>108003.8771958204</v>
+        <v>110258.0600029897</v>
       </c>
     </row>
     <row r="389">
@@ -4711,7 +4711,7 @@
         <v>113773.3411916541</v>
       </c>
       <c r="C389" t="n">
-        <v>107511.5357707427</v>
+        <v>109742.2858132963</v>
       </c>
     </row>
     <row r="390">
@@ -4722,7 +4722,7 @@
         <v>114241.0114653265</v>
       </c>
       <c r="C390" t="n">
-        <v>107693.8863665741</v>
+        <v>109921.425927891</v>
       </c>
     </row>
     <row r="391">
@@ -4733,7 +4733,7 @@
         <v>114405.8973495482</v>
       </c>
       <c r="C391" t="n">
-        <v>107464.7248583838</v>
+        <v>109726.2314609184</v>
       </c>
     </row>
     <row r="392">
@@ -4744,7 +4744,7 @@
         <v>113681.9888799965</v>
       </c>
       <c r="C392" t="n">
-        <v>107202.8520240434</v>
+        <v>109449.5610652058</v>
       </c>
     </row>
     <row r="393">
@@ -4755,7 +4755,7 @@
         <v>113719.1152807076</v>
       </c>
       <c r="C393" t="n">
-        <v>107368.5873952462</v>
+        <v>109565.2614805851</v>
       </c>
     </row>
     <row r="394">
@@ -4766,7 +4766,7 @@
         <v>114319.7795718064</v>
       </c>
       <c r="C394" t="n">
-        <v>107316.0507939635</v>
+        <v>109626.67819023</v>
       </c>
     </row>
     <row r="395">
@@ -4777,7 +4777,7 @@
         <v>114029.496095481</v>
       </c>
       <c r="C395" t="n">
-        <v>107195.6858803139</v>
+        <v>109594.4796275884</v>
       </c>
     </row>
     <row r="396">
@@ -4788,7 +4788,7 @@
         <v>114324.1651662702</v>
       </c>
       <c r="C396" t="n">
-        <v>107414.2903794321</v>
+        <v>109608.3598116475</v>
       </c>
     </row>
     <row r="397">
@@ -4799,7 +4799,7 @@
         <v>115401.3434040633</v>
       </c>
       <c r="C397" t="n">
-        <v>108669.1363830427</v>
+        <v>110507.5466752255</v>
       </c>
     </row>
     <row r="398">
@@ -4810,7 +4810,7 @@
         <v>114475.9942557552</v>
       </c>
       <c r="C398" t="n">
-        <v>108356.496040821</v>
+        <v>110287.9225504705</v>
       </c>
     </row>
     <row r="399">
@@ -4821,7 +4821,7 @@
         <v>113732.9363214024</v>
       </c>
       <c r="C399" t="n">
-        <v>108143.9133201245</v>
+        <v>110342.6457661912</v>
       </c>
     </row>
     <row r="400">
@@ -4832,7 +4832,7 @@
         <v>112553.8515574565</v>
       </c>
       <c r="C400" t="n">
-        <v>107722.0440791114</v>
+        <v>109961.496715085</v>
       </c>
     </row>
     <row r="401">
@@ -4843,7 +4843,7 @@
         <v>112289.8175649288</v>
       </c>
       <c r="C401" t="n">
-        <v>107063.9317705172</v>
+        <v>109448.0130528097</v>
       </c>
     </row>
     <row r="402">
@@ -4854,7 +4854,7 @@
         <v>112183.0559388261</v>
       </c>
       <c r="C402" t="n">
-        <v>107307.3807336958</v>
+        <v>109503.673737762</v>
       </c>
     </row>
     <row r="403">
@@ -4865,7 +4865,7 @@
         <v>113211.0942183313</v>
       </c>
       <c r="C403" t="n">
-        <v>107642.6446634476</v>
+        <v>109976.0841300576</v>
       </c>
     </row>
     <row r="404">
@@ -4876,7 +4876,7 @@
         <v>113471.6765156745</v>
       </c>
       <c r="C404" t="n">
-        <v>108026.8175040275</v>
+        <v>110298.1005282593</v>
       </c>
     </row>
     <row r="405">
@@ -4887,7 +4887,7 @@
         <v>113947.4330384336</v>
       </c>
       <c r="C405" t="n">
-        <v>108493.8769082941</v>
+        <v>110727.3503849634</v>
       </c>
     </row>
     <row r="406">
@@ -4898,7 +4898,7 @@
         <v>114268.2244643728</v>
       </c>
       <c r="C406" t="n">
-        <v>108490.0571821217</v>
+        <v>110914.0410711352</v>
       </c>
     </row>
     <row r="407">
@@ -4909,7 +4909,7 @@
         <v>113935.2518638</v>
       </c>
       <c r="C407" t="n">
-        <v>108427.8226958925</v>
+        <v>110827.8268559799</v>
       </c>
     </row>
     <row r="408">
@@ -4920,7 +4920,7 @@
         <v>114580.780531652</v>
       </c>
       <c r="C408" t="n">
-        <v>108529.9421669411</v>
+        <v>110914.0025689181</v>
       </c>
     </row>
     <row r="409">
@@ -4931,7 +4931,7 @@
         <v>115154.5459985403</v>
       </c>
       <c r="C409" t="n">
-        <v>108540.9924520639</v>
+        <v>111029.2165554212</v>
       </c>
     </row>
     <row r="410">
@@ -4942,7 +4942,7 @@
         <v>115368.2557477571</v>
       </c>
       <c r="C410" t="n">
-        <v>108514.0739130233</v>
+        <v>111015.6357963055</v>
       </c>
     </row>
     <row r="411">
@@ -4953,7 +4953,7 @@
         <v>115244.6326802314</v>
       </c>
       <c r="C411" t="n">
-        <v>108558.24654472</v>
+        <v>111089.0630743882</v>
       </c>
     </row>
     <row r="412">
@@ -4964,7 +4964,7 @@
         <v>115505.6372386449</v>
       </c>
       <c r="C412" t="n">
-        <v>108568.5822470607</v>
+        <v>111113.0491046033</v>
       </c>
     </row>
     <row r="413">
@@ -4975,7 +4975,7 @@
         <v>114800.7618185492</v>
       </c>
       <c r="C413" t="n">
-        <v>108210.1651786862</v>
+        <v>110705.5245747161</v>
       </c>
     </row>
     <row r="414">
@@ -4986,7 +4986,7 @@
         <v>116309.8329588428</v>
       </c>
       <c r="C414" t="n">
-        <v>109111.433103872</v>
+        <v>111605.2328956102</v>
       </c>
     </row>
     <row r="415">
@@ -4997,7 +4997,7 @@
         <v>116497.7946356085</v>
       </c>
       <c r="C415" t="n">
-        <v>109306.9131045579</v>
+        <v>111774.9835255679</v>
       </c>
     </row>
     <row r="416">
@@ -5008,7 +5008,7 @@
         <v>116289.3374200198</v>
       </c>
       <c r="C416" t="n">
-        <v>109142.6863721644</v>
+        <v>111620.3615252348</v>
       </c>
     </row>
     <row r="417">
@@ -5019,7 +5019,7 @@
         <v>115747.4600253278</v>
       </c>
       <c r="C417" t="n">
-        <v>108756.8782620089</v>
+        <v>111234.8866153503</v>
       </c>
     </row>
     <row r="418">
@@ -5030,7 +5030,7 @@
         <v>116164.4714190602</v>
       </c>
       <c r="C418" t="n">
-        <v>109011.0225028683</v>
+        <v>111483.9843368188</v>
       </c>
     </row>
     <row r="419">
@@ -5041,7 +5041,7 @@
         <v>115932.6531696029</v>
       </c>
       <c r="C419" t="n">
-        <v>108685.9325481851</v>
+        <v>111159.0034466224</v>
       </c>
     </row>
     <row r="420">
@@ -5052,7 +5052,7 @@
         <v>114861.1185713116</v>
       </c>
       <c r="C420" t="n">
-        <v>108168.4221982583</v>
+        <v>110656.8756024569</v>
       </c>
     </row>
     <row r="421">
@@ -5063,7 +5063,7 @@
         <v>114895.9872013169</v>
       </c>
       <c r="C421" t="n">
-        <v>108224.4292528606</v>
+        <v>110727.9392353727</v>
       </c>
     </row>
     <row r="422">
@@ -5074,7 +5074,7 @@
         <v>115137.2265966423</v>
       </c>
       <c r="C422" t="n">
-        <v>108458.3846951013</v>
+        <v>110977.6767697213</v>
       </c>
     </row>
     <row r="423">
@@ -5085,7 +5085,7 @@
         <v>114349.0885754762</v>
       </c>
       <c r="C423" t="n">
-        <v>108076.7308546988</v>
+        <v>110601.371481091</v>
       </c>
     </row>
     <row r="424">
@@ -5096,7 +5096,7 @@
         <v>114621.7612588311</v>
       </c>
       <c r="C424" t="n">
-        <v>108261.9405131565</v>
+        <v>110793.9977673555</v>
       </c>
     </row>
     <row r="425">
@@ -5107,7 +5107,7 @@
         <v>114561.6485844044</v>
       </c>
       <c r="C425" t="n">
-        <v>107992.9395681738</v>
+        <v>110562.2512548933</v>
       </c>
     </row>
     <row r="426">
@@ -5118,7 +5118,7 @@
         <v>114763.2581365181</v>
       </c>
       <c r="C426" t="n">
-        <v>108285.5964987831</v>
+        <v>110837.6315186376</v>
       </c>
     </row>
     <row r="427">
@@ -5129,7 +5129,7 @@
         <v>115738.3020114776</v>
       </c>
       <c r="C427" t="n">
-        <v>108821.3585971783</v>
+        <v>111381.7307380931</v>
       </c>
     </row>
     <row r="428">
@@ -5140,7 +5140,7 @@
         <v>116646.6735202074</v>
       </c>
       <c r="C428" t="n">
-        <v>109067.9107563005</v>
+        <v>111653.1023874753</v>
       </c>
     </row>
     <row r="429">
@@ -5151,7 +5151,7 @@
         <v>117014.3487657758</v>
       </c>
       <c r="C429" t="n">
-        <v>109518.6009031567</v>
+        <v>112096.7204323983</v>
       </c>
     </row>
     <row r="430">
@@ -5162,7 +5162,7 @@
         <v>117144.2666647298</v>
       </c>
       <c r="C430" t="n">
-        <v>109667.2545382937</v>
+        <v>112218.342059301</v>
       </c>
     </row>
     <row r="431">
@@ -5173,7 +5173,7 @@
         <v>116761.0732069091</v>
       </c>
       <c r="C431" t="n">
-        <v>109339.2830551219</v>
+        <v>111879.8606028899</v>
       </c>
     </row>
     <row r="432">
@@ -5184,7 +5184,7 @@
         <v>117935.0597796377</v>
       </c>
       <c r="C432" t="n">
-        <v>109953.5228296053</v>
+        <v>112501.7197423781</v>
       </c>
     </row>
     <row r="433">
@@ -5195,7 +5195,7 @@
         <v>117963.3049304491</v>
       </c>
       <c r="C433" t="n">
-        <v>109909.6607803175</v>
+        <v>112487.7324800329</v>
       </c>
     </row>
     <row r="434">
@@ -5206,7 +5206,7 @@
         <v>117870.4741866133</v>
       </c>
       <c r="C434" t="n">
-        <v>109830.1089545957</v>
+        <v>112409.8801711527</v>
       </c>
     </row>
     <row r="435">
@@ -5217,7 +5217,7 @@
         <v>118555.1284861441</v>
       </c>
       <c r="C435" t="n">
-        <v>110364.5332615616</v>
+        <v>112949.3368867998</v>
       </c>
     </row>
     <row r="436">
@@ -5228,7 +5228,7 @@
         <v>117994.7204975954</v>
       </c>
       <c r="C436" t="n">
-        <v>109891.6059781545</v>
+        <v>112538.5678267548</v>
       </c>
     </row>
     <row r="437">
@@ -5239,7 +5239,7 @@
         <v>118114.6563119525</v>
       </c>
       <c r="C437" t="n">
-        <v>110072.1864788529</v>
+        <v>112371.657625856</v>
       </c>
     </row>
     <row r="438">
@@ -5250,7 +5250,7 @@
         <v>118243.6143496417</v>
       </c>
       <c r="C438" t="n">
-        <v>109990.7133566882</v>
+        <v>112612.2205601218</v>
       </c>
     </row>
     <row r="439">
@@ -5261,7 +5261,7 @@
         <v>118064.0531833417</v>
       </c>
       <c r="C439" t="n">
-        <v>109756.5623784485</v>
+        <v>112517.1141627234</v>
       </c>
     </row>
     <row r="440">
@@ -5272,7 +5272,7 @@
         <v>118415.4653438082</v>
       </c>
       <c r="C440" t="n">
-        <v>110207.2631897721</v>
+        <v>113154.2707558498</v>
       </c>
     </row>
     <row r="441">
@@ -5283,7 +5283,7 @@
         <v>118449.709778988</v>
       </c>
       <c r="C441" t="n">
-        <v>110099.2585982232</v>
+        <v>113251.2283978089</v>
       </c>
     </row>
     <row r="442">
@@ -5294,7 +5294,7 @@
         <v>118365.1085715601</v>
       </c>
       <c r="C442" t="n">
-        <v>109843.5938439636</v>
+        <v>113376.1222330368</v>
       </c>
     </row>
     <row r="443">
@@ -5305,7 +5305,7 @@
         <v>118469.9741637823</v>
       </c>
       <c r="C443" t="n">
-        <v>109514.9180550397</v>
+        <v>113154.9530742194</v>
       </c>
     </row>
     <row r="444">
@@ -5316,7 +5316,7 @@
         <v>118307.0532226962</v>
       </c>
       <c r="C444" t="n">
-        <v>109214.1513145933</v>
+        <v>113271.2091804514</v>
       </c>
     </row>
     <row r="445">
@@ -5327,7 +5327,7 @@
         <v>117810.6890433606</v>
       </c>
       <c r="C445" t="n">
-        <v>109105.458210233</v>
+        <v>112753.3243976714</v>
       </c>
     </row>
     <row r="446">
@@ -5338,7 +5338,7 @@
         <v>117504.5806828084</v>
       </c>
       <c r="C446" t="n">
-        <v>108842.1891895374</v>
+        <v>112401.5570868612</v>
       </c>
     </row>
     <row r="447">
@@ -5349,7 +5349,7 @@
         <v>117847.2149746765</v>
       </c>
       <c r="C447" t="n">
-        <v>108987.0002235165</v>
+        <v>112852.6563472209</v>
       </c>
     </row>
     <row r="448">
@@ -5360,7 +5360,7 @@
         <v>118590.2957927317</v>
       </c>
       <c r="C448" t="n">
-        <v>109334.7653844089</v>
+        <v>112963.7737363859</v>
       </c>
     </row>
     <row r="449">
@@ -5371,7 +5371,7 @@
         <v>118480.1677349138</v>
       </c>
       <c r="C449" t="n">
-        <v>109330.3125312336</v>
+        <v>112614.5186922706</v>
       </c>
     </row>
     <row r="450">
@@ -5382,7 +5382,7 @@
         <v>118387.0332714788</v>
       </c>
       <c r="C450" t="n">
-        <v>109553.8845489428</v>
+        <v>112341.082897968</v>
       </c>
     </row>
     <row r="451">
@@ -5393,7 +5393,7 @@
         <v>118901.4074857414</v>
       </c>
       <c r="C451" t="n">
-        <v>109590.8364282611</v>
+        <v>112418.0530122577</v>
       </c>
     </row>
     <row r="452">
@@ -5404,7 +5404,7 @@
         <v>118792.0600886933</v>
       </c>
       <c r="C452" t="n">
-        <v>109319.5634359135</v>
+        <v>112163.7280268076</v>
       </c>
     </row>
     <row r="453">
@@ -5415,7 +5415,7 @@
         <v>118978.7934451394</v>
       </c>
       <c r="C453" t="n">
-        <v>109262.7282447847</v>
+        <v>112187.3175818528</v>
       </c>
     </row>
     <row r="454">
@@ -5426,7 +5426,7 @@
         <v>118360.0420299284</v>
       </c>
       <c r="C454" t="n">
-        <v>108896.151376597</v>
+        <v>111794.5057624734</v>
       </c>
     </row>
     <row r="455">
@@ -5437,7 +5437,7 @@
         <v>118787.2497671331</v>
       </c>
       <c r="C455" t="n">
-        <v>109320.2218873799</v>
+        <v>112197.1089383817</v>
       </c>
     </row>
     <row r="456">
@@ -5448,7 +5448,7 @@
         <v>118079.0498713159</v>
       </c>
       <c r="C456" t="n">
-        <v>108994.5932299615</v>
+        <v>111829.2763847423</v>
       </c>
     </row>
     <row r="457">
@@ -5459,7 +5459,7 @@
         <v>118418.9070470187</v>
       </c>
       <c r="C457" t="n">
-        <v>109140.4322519661</v>
+        <v>112019.9914058676</v>
       </c>
     </row>
     <row r="458">
@@ -5470,7 +5470,7 @@
         <v>118474.0854962629</v>
       </c>
       <c r="C458" t="n">
-        <v>109287.2288396292</v>
+        <v>112139.2826687621</v>
       </c>
     </row>
     <row r="459">
@@ -5481,7 +5481,7 @@
         <v>118385.2423283314</v>
       </c>
       <c r="C459" t="n">
-        <v>108553.2194168111</v>
+        <v>111547.330768774</v>
       </c>
     </row>
     <row r="460">
@@ -5492,7 +5492,7 @@
         <v>118613.8538182497</v>
       </c>
       <c r="C460" t="n">
-        <v>108590.1514270133</v>
+        <v>111650.735986793</v>
       </c>
     </row>
     <row r="461">
@@ -5503,7 +5503,7 @@
         <v>118891.6330528292</v>
       </c>
       <c r="C461" t="n">
-        <v>108878.9154775958</v>
+        <v>111904.9253367271</v>
       </c>
     </row>
     <row r="462">
@@ -5514,7 +5514,7 @@
         <v>118135.0510172024</v>
       </c>
       <c r="C462" t="n">
-        <v>108899.3770681979</v>
+        <v>111798.1670868118</v>
       </c>
     </row>
     <row r="463">
@@ -5525,7 +5525,7 @@
         <v>117840.9695940388</v>
       </c>
       <c r="C463" t="n">
-        <v>108409.1042019316</v>
+        <v>111336.4700559806</v>
       </c>
     </row>
     <row r="464">
@@ -5536,7 +5536,7 @@
         <v>118419.7811479043</v>
       </c>
       <c r="C464" t="n">
-        <v>109096.9186965251</v>
+        <v>111953.0570514435</v>
       </c>
     </row>
     <row r="465">
@@ -5547,7 +5547,7 @@
         <v>119088.8323367743</v>
       </c>
       <c r="C465" t="n">
-        <v>109416.6712978187</v>
+        <v>112280.256965055</v>
       </c>
     </row>
     <row r="466">
@@ -5558,7 +5558,7 @@
         <v>119225.6002085128</v>
       </c>
       <c r="C466" t="n">
-        <v>108804.6362413505</v>
+        <v>111660.690905521</v>
       </c>
     </row>
     <row r="467">
@@ -5569,7 +5569,7 @@
         <v>120045.3036578751</v>
       </c>
       <c r="C467" t="n">
-        <v>109588.5234539672</v>
+        <v>112472.5766360098</v>
       </c>
     </row>
     <row r="468">
@@ -5580,7 +5580,7 @@
         <v>119895.5657825012</v>
       </c>
       <c r="C468" t="n">
-        <v>109311.1514044393</v>
+        <v>112277.8024101002</v>
       </c>
     </row>
     <row r="469">
@@ -5591,7 +5591,7 @@
         <v>119342.2977716323</v>
       </c>
       <c r="C469" t="n">
-        <v>108767.0293026012</v>
+        <v>111733.7054325151</v>
       </c>
     </row>
     <row r="470">
@@ -5602,7 +5602,7 @@
         <v>118375.2458383965</v>
       </c>
       <c r="C470" t="n">
-        <v>108246.8396050408</v>
+        <v>111159.2010403571</v>
       </c>
     </row>
     <row r="471">
@@ -5613,7 +5613,7 @@
         <v>117825.3390463479</v>
       </c>
       <c r="C471" t="n">
-        <v>108116.0138637556</v>
+        <v>110971.4591702833</v>
       </c>
     </row>
     <row r="472">
@@ -5624,7 +5624,7 @@
         <v>117385.7471142085</v>
       </c>
       <c r="C472" t="n">
-        <v>108017.854366766</v>
+        <v>110815.480394713</v>
       </c>
     </row>
     <row r="473">
@@ -5635,7 +5635,7 @@
         <v>116904.6760127855</v>
       </c>
       <c r="C473" t="n">
-        <v>107856.0339875852</v>
+        <v>110622.6095705925</v>
       </c>
     </row>
     <row r="474">
@@ -5646,7 +5646,7 @@
         <v>117794.9278752805</v>
       </c>
       <c r="C474" t="n">
-        <v>108535.5077306725</v>
+        <v>111223.7513300067</v>
       </c>
     </row>
     <row r="475">
@@ -5657,7 +5657,7 @@
         <v>118351.2147383304</v>
       </c>
       <c r="C475" t="n">
-        <v>108803.1822466292</v>
+        <v>111534.5657172213</v>
       </c>
     </row>
     <row r="476">
@@ -5668,7 +5668,7 @@
         <v>118492.7845932596</v>
       </c>
       <c r="C476" t="n">
-        <v>108768.9191106354</v>
+        <v>111527.5498712134</v>
       </c>
     </row>
     <row r="477">
@@ -5679,7 +5679,7 @@
         <v>119152.0106011816</v>
       </c>
       <c r="C477" t="n">
-        <v>108962.941556431</v>
+        <v>111760.7974026221</v>
       </c>
     </row>
     <row r="478">
@@ -5690,7 +5690,7 @@
         <v>119892.8126720526</v>
       </c>
       <c r="C478" t="n">
-        <v>108974.7155711107</v>
+        <v>111884.1499040159</v>
       </c>
     </row>
     <row r="479">
@@ -5701,7 +5701,7 @@
         <v>119650.8642177623</v>
       </c>
       <c r="C479" t="n">
-        <v>109099.5685241374</v>
+        <v>112079.3303383081</v>
       </c>
     </row>
     <row r="480">
@@ -5712,7 +5712,7 @@
         <v>119463.2984590972</v>
       </c>
       <c r="C480" t="n">
-        <v>109014.2575682921</v>
+        <v>111967.5850053069</v>
       </c>
     </row>
     <row r="481">
@@ -5723,7 +5723,7 @@
         <v>119582.3805767287</v>
       </c>
       <c r="C481" t="n">
-        <v>109045.3038625437</v>
+        <v>112054.1316562085</v>
       </c>
     </row>
     <row r="482">
@@ -5734,7 +5734,7 @@
         <v>120022.507873297</v>
       </c>
       <c r="C482" t="n">
-        <v>109261.0936750796</v>
+        <v>112315.0027591451</v>
       </c>
     </row>
     <row r="483">
@@ -5745,7 +5745,7 @@
         <v>119676.1712898762</v>
       </c>
       <c r="C483" t="n">
-        <v>109057.3152399566</v>
+        <v>112127.67636074</v>
       </c>
     </row>
     <row r="484">
@@ -5756,7 +5756,7 @@
         <v>119703.8074354585</v>
       </c>
       <c r="C484" t="n">
-        <v>109308.6711011484</v>
+        <v>112277.1379562583</v>
       </c>
     </row>
     <row r="485">
@@ -5767,7 +5767,7 @@
         <v>119908.2795151175</v>
       </c>
       <c r="C485" t="n">
-        <v>109304.1824405885</v>
+        <v>112395.5400623269</v>
       </c>
     </row>
     <row r="486">
@@ -5778,7 +5778,7 @@
         <v>119466.9756011377</v>
       </c>
       <c r="C486" t="n">
-        <v>109076.1153598981</v>
+        <v>112338.7366639456</v>
       </c>
     </row>
     <row r="487">
@@ -5789,7 +5789,7 @@
         <v>119560.3285746274</v>
       </c>
       <c r="C487" t="n">
-        <v>108962.8226523539</v>
+        <v>112384.7066695655</v>
       </c>
     </row>
     <row r="488">
@@ -5800,7 +5800,7 @@
         <v>119733.5015811379</v>
       </c>
       <c r="C488" t="n">
-        <v>109414.6979878433</v>
+        <v>112447.1275316966</v>
       </c>
     </row>
     <row r="489">
@@ -5811,7 +5811,7 @@
         <v>119931.1076857707</v>
       </c>
       <c r="C489" t="n">
-        <v>109807.4941015238</v>
+        <v>112446.2384965299</v>
       </c>
     </row>
     <row r="490">
@@ -5822,7 +5822,7 @@
         <v>120423.9551635154</v>
       </c>
       <c r="C490" t="n">
-        <v>110363.7200839393</v>
+        <v>112684.2358733802</v>
       </c>
     </row>
     <row r="491">
@@ -5833,7 +5833,7 @@
         <v>119522.5652369661</v>
       </c>
       <c r="C491" t="n">
-        <v>109736.1513895489</v>
+        <v>112236.7633786806</v>
       </c>
     </row>
     <row r="492">
@@ -5844,7 +5844,7 @@
         <v>118897.6702444919</v>
       </c>
       <c r="C492" t="n">
-        <v>109234.2190764255</v>
+        <v>111905.6392397713</v>
       </c>
     </row>
     <row r="493">
@@ -5855,7 +5855,7 @@
         <v>119044.716235357</v>
       </c>
       <c r="C493" t="n">
-        <v>109149.0674383873</v>
+        <v>111889.8039854245</v>
       </c>
     </row>
     <row r="494">
@@ -5866,7 +5866,7 @@
         <v>118571.6779929372</v>
       </c>
       <c r="C494" t="n">
-        <v>108954.5658037594</v>
+        <v>111679.2710284032</v>
       </c>
     </row>
     <row r="495">
@@ -5877,7 +5877,7 @@
         <v>116527.946555901</v>
       </c>
       <c r="C495" t="n">
-        <v>108090.2587690384</v>
+        <v>110614.863719827</v>
       </c>
     </row>
     <row r="496">
@@ -5888,7 +5888,7 @@
         <v>116335.5284987559</v>
       </c>
       <c r="C496" t="n">
-        <v>107905.085483918</v>
+        <v>110411.7783403652</v>
       </c>
     </row>
     <row r="497">
@@ -5899,7 +5899,7 @@
         <v>117077.8376064709</v>
       </c>
       <c r="C497" t="n">
-        <v>108353.0245976757</v>
+        <v>110893.9193853175</v>
       </c>
     </row>
     <row r="498">
@@ -5910,7 +5910,7 @@
         <v>116823.8389350677</v>
       </c>
       <c r="C498" t="n">
-        <v>108220.3937187576</v>
+        <v>110728.8287588671</v>
       </c>
     </row>
     <row r="499">
@@ -5921,7 +5921,7 @@
         <v>117275.1192177733</v>
       </c>
       <c r="C499" t="n">
-        <v>108541.2024289001</v>
+        <v>111057.4303284452</v>
       </c>
     </row>
     <row r="500">
@@ -5932,7 +5932,7 @@
         <v>117610.1815645677</v>
       </c>
       <c r="C500" t="n">
-        <v>108460.4218375046</v>
+        <v>111055.8467521814</v>
       </c>
     </row>
     <row r="501">
@@ -5943,7 +5943,7 @@
         <v>117093.5215019378</v>
       </c>
       <c r="C501" t="n">
-        <v>108437.3191368838</v>
+        <v>110918.9695279442</v>
       </c>
     </row>
     <row r="502">
@@ -5954,7 +5954,7 @@
         <v>117105.2417520511</v>
       </c>
       <c r="C502" t="n">
-        <v>108845.5473099095</v>
+        <v>111233.450407781</v>
       </c>
     </row>
     <row r="503">
@@ -5965,7 +5965,7 @@
         <v>117298.2862037623</v>
       </c>
       <c r="C503" t="n">
-        <v>108893.0025519255</v>
+        <v>111268.310937381</v>
       </c>
     </row>
     <row r="504">
@@ -5976,7 +5976,7 @@
         <v>117873.3869767516</v>
       </c>
       <c r="C504" t="n">
-        <v>109271.0871020608</v>
+        <v>111627.385731107</v>
       </c>
     </row>
     <row r="505">
@@ -5987,7 +5987,7 @@
         <v>117943.4432877119</v>
       </c>
       <c r="C505" t="n">
-        <v>109151.1547738243</v>
+        <v>111579.5134525303</v>
       </c>
     </row>
     <row r="506">
@@ -5998,7 +5998,7 @@
         <v>117948.4757366857</v>
       </c>
       <c r="C506" t="n">
-        <v>109192.4553221232</v>
+        <v>111605.8810737907</v>
       </c>
     </row>
     <row r="507">
@@ -6009,7 +6009,7 @@
         <v>117844.1394696291</v>
       </c>
       <c r="C507" t="n">
-        <v>109119.4342594374</v>
+        <v>111473.9453897863</v>
       </c>
     </row>
     <row r="508">
@@ -6020,7 +6020,7 @@
         <v>117875.4792526654</v>
       </c>
       <c r="C508" t="n">
-        <v>109120.4535646925</v>
+        <v>111478.4642548884</v>
       </c>
     </row>
     <row r="509">
@@ -6031,7 +6031,7 @@
         <v>117876.0336302278</v>
       </c>
       <c r="C509" t="n">
-        <v>109576.5664885292</v>
+        <v>111677.9188096865</v>
       </c>
     </row>
     <row r="510">
@@ -6042,7 +6042,7 @@
         <v>117757.0908456099</v>
       </c>
       <c r="C510" t="n">
-        <v>109718.2293548986</v>
+        <v>111757.8226765834</v>
       </c>
     </row>
     <row r="511">
@@ -6053,7 +6053,7 @@
         <v>118161.2067064564</v>
       </c>
       <c r="C511" t="n">
-        <v>109766.6725898303</v>
+        <v>111873.8929216278</v>
       </c>
     </row>
     <row r="512">
@@ -6064,7 +6064,7 @@
         <v>119409.4458597987</v>
       </c>
       <c r="C512" t="n">
-        <v>110756.028301324</v>
+        <v>112876.814846099</v>
       </c>
     </row>
     <row r="513">
@@ -6075,7 +6075,7 @@
         <v>119557.2024654581</v>
       </c>
       <c r="C513" t="n">
-        <v>110649.430103319</v>
+        <v>112823.1874096633</v>
       </c>
     </row>
     <row r="514">
@@ -6086,7 +6086,7 @@
         <v>119497.0723754243</v>
       </c>
       <c r="C514" t="n">
-        <v>110599.5281267552</v>
+        <v>112814.0733132732</v>
       </c>
     </row>
     <row r="515">
@@ -6097,7 +6097,7 @@
         <v>120404.2277731841</v>
       </c>
       <c r="C515" t="n">
-        <v>110738.6546222575</v>
+        <v>113138.508630544</v>
       </c>
     </row>
     <row r="516">
@@ -6108,7 +6108,7 @@
         <v>120276.095402117</v>
       </c>
       <c r="C516" t="n">
-        <v>110579.339500312</v>
+        <v>112964.6826467723</v>
       </c>
     </row>
     <row r="517">
@@ -6119,7 +6119,7 @@
         <v>120254.2495840677</v>
       </c>
       <c r="C517" t="n">
-        <v>110437.8361890639</v>
+        <v>112868.1005408303</v>
       </c>
     </row>
     <row r="518">
@@ -6130,7 +6130,7 @@
         <v>120426.5727042743</v>
       </c>
       <c r="C518" t="n">
-        <v>110560.2330053493</v>
+        <v>112993.5751923581</v>
       </c>
     </row>
     <row r="519">
@@ -6141,7 +6141,7 @@
         <v>119844.7255981047</v>
       </c>
       <c r="C519" t="n">
-        <v>110374.8734231476</v>
+        <v>112844.6792491278</v>
       </c>
     </row>
     <row r="520">
@@ -6152,7 +6152,7 @@
         <v>120081.1721695339</v>
       </c>
       <c r="C520" t="n">
-        <v>110372.7865845031</v>
+        <v>112867.1128186694</v>
       </c>
     </row>
     <row r="521">
@@ -6163,7 +6163,7 @@
         <v>119939.3765941043</v>
       </c>
       <c r="C521" t="n">
-        <v>110385.9443546927</v>
+        <v>112843.3723381315</v>
       </c>
     </row>
     <row r="522">
@@ -6174,7 +6174,7 @@
         <v>120665.8421830796</v>
       </c>
       <c r="C522" t="n">
-        <v>110567.4898219457</v>
+        <v>113116.6443211686</v>
       </c>
     </row>
     <row r="523">
@@ -6185,7 +6185,7 @@
         <v>120397.1270924094</v>
       </c>
       <c r="C523" t="n">
-        <v>110394.6206130295</v>
+        <v>112913.7139442179</v>
       </c>
     </row>
     <row r="524">
@@ -6196,7 +6196,7 @@
         <v>120449.2944129838</v>
       </c>
       <c r="C524" t="n">
-        <v>110679.622257083</v>
+        <v>113098.875267091</v>
       </c>
     </row>
     <row r="525">
@@ -6207,7 +6207,7 @@
         <v>121147.0275047179</v>
       </c>
       <c r="C525" t="n">
-        <v>110893.7826427903</v>
+        <v>113394.7004043701</v>
       </c>
     </row>
     <row r="526">
@@ -6218,7 +6218,7 @@
         <v>121647.2958630012</v>
       </c>
       <c r="C526" t="n">
-        <v>111017.9685300434</v>
+        <v>113646.5327018002</v>
       </c>
     </row>
     <row r="527">
@@ -6229,7 +6229,7 @@
         <v>121478.7668903188</v>
       </c>
       <c r="C527" t="n">
-        <v>110980.2095341154</v>
+        <v>113579.2625514208</v>
       </c>
     </row>
     <row r="528">
@@ -6240,7 +6240,7 @@
         <v>121144.6768772768</v>
       </c>
       <c r="C528" t="n">
-        <v>110809.5061693227</v>
+        <v>113346.9759847676</v>
       </c>
     </row>
     <row r="529">
@@ -6251,7 +6251,7 @@
         <v>121932.4745280278</v>
       </c>
       <c r="C529" t="n">
-        <v>111221.9540545055</v>
+        <v>113725.2012702898</v>
       </c>
     </row>
     <row r="530">
@@ -6262,7 +6262,7 @@
         <v>121721.856904723</v>
       </c>
       <c r="C530" t="n">
-        <v>111270.8696206495</v>
+        <v>113671.6760237883</v>
       </c>
     </row>
     <row r="531">
@@ -6273,7 +6273,7 @@
         <v>121197.3894614676</v>
       </c>
       <c r="C531" t="n">
-        <v>110726.6931200618</v>
+        <v>113163.7368697797</v>
       </c>
     </row>
     <row r="532">
@@ -6284,7 +6284,7 @@
         <v>122060.8853668664</v>
       </c>
       <c r="C532" t="n">
-        <v>111262.5698369396</v>
+        <v>113758.3255267382</v>
       </c>
     </row>
     <row r="533">
@@ -6295,7 +6295,7 @@
         <v>121786.6785532582</v>
       </c>
       <c r="C533" t="n">
-        <v>111461.0536408637</v>
+        <v>113907.696288024</v>
       </c>
     </row>
     <row r="534">
@@ -6306,7 +6306,7 @@
         <v>122439.2090154848</v>
       </c>
       <c r="C534" t="n">
-        <v>111652.3388582098</v>
+        <v>114056.682187256</v>
       </c>
     </row>
     <row r="535">
@@ -6317,7 +6317,7 @@
         <v>122548.8185577207</v>
       </c>
       <c r="C535" t="n">
-        <v>111925.3787653652</v>
+        <v>114247.7698193599</v>
       </c>
     </row>
     <row r="536">
@@ -6328,7 +6328,7 @@
         <v>122432.3916204175</v>
       </c>
       <c r="C536" t="n">
-        <v>112051.8225610124</v>
+        <v>114323.9281871439</v>
       </c>
     </row>
     <row r="537">
@@ -6339,7 +6339,7 @@
         <v>121618.0310990509</v>
       </c>
       <c r="C537" t="n">
-        <v>111802.5252774225</v>
+        <v>114070.0245093333</v>
       </c>
     </row>
     <row r="538">
@@ -6350,7 +6350,7 @@
         <v>121592.8698018062</v>
       </c>
       <c r="C538" t="n">
-        <v>111775.8811767623</v>
+        <v>114071.8835570842</v>
       </c>
     </row>
     <row r="539">
@@ -6361,7 +6361,7 @@
         <v>121212.7108635124</v>
       </c>
       <c r="C539" t="n">
-        <v>111827.7739892039</v>
+        <v>114147.597393815</v>
       </c>
     </row>
     <row r="540">
@@ -6372,7 +6372,7 @@
         <v>121226.6909093009</v>
       </c>
       <c r="C540" t="n">
-        <v>111729.7758178068</v>
+        <v>114139.6902297788</v>
       </c>
     </row>
     <row r="541">
@@ -6383,7 +6383,7 @@
         <v>120437.0820181778</v>
       </c>
       <c r="C541" t="n">
-        <v>111582.9927605373</v>
+        <v>113827.9691527637</v>
       </c>
     </row>
     <row r="542">
@@ -6394,7 +6394,7 @@
         <v>120574.2031424644</v>
       </c>
       <c r="C542" t="n">
-        <v>112178.6131088228</v>
+        <v>114192.1504555842</v>
       </c>
     </row>
     <row r="543">
@@ -6405,7 +6405,7 @@
         <v>120228.1981818429</v>
       </c>
       <c r="C543" t="n">
-        <v>111417.2479112425</v>
+        <v>113805.0668210429</v>
       </c>
     </row>
     <row r="544">
@@ -6416,7 +6416,7 @@
         <v>120193.6633998617</v>
       </c>
       <c r="C544" t="n">
-        <v>110986.8329303835</v>
+        <v>113642.5441132327</v>
       </c>
     </row>
     <row r="545">
@@ -6427,7 +6427,7 @@
         <v>120336.7926948931</v>
       </c>
       <c r="C545" t="n">
-        <v>111152.7954941553</v>
+        <v>113843.9303858723</v>
       </c>
     </row>
     <row r="546">
@@ -6438,7 +6438,7 @@
         <v>119672.4708275078</v>
       </c>
       <c r="C546" t="n">
-        <v>110548.0791975102</v>
+        <v>113226.6660948313</v>
       </c>
     </row>
     <row r="547">
@@ -6449,7 +6449,7 @@
         <v>119941.1154032586</v>
       </c>
       <c r="C547" t="n">
-        <v>110694.8000718448</v>
+        <v>113382.7141321171</v>
       </c>
     </row>
     <row r="548">
@@ -6460,7 +6460,7 @@
         <v>119153.5527405131</v>
       </c>
       <c r="C548" t="n">
-        <v>110107.6106310129</v>
+        <v>112649.5965930022</v>
       </c>
     </row>
     <row r="549">
@@ -6471,7 +6471,7 @@
         <v>119441.6982689776</v>
       </c>
       <c r="C549" t="n">
-        <v>109950.2433926968</v>
+        <v>112865.7484701421</v>
       </c>
     </row>
     <row r="550">
@@ -6482,7 +6482,7 @@
         <v>119548.5705804438</v>
       </c>
       <c r="C550" t="n">
-        <v>109935.8738433109</v>
+        <v>112938.5154591529</v>
       </c>
     </row>
     <row r="551">
@@ -6493,7 +6493,7 @@
         <v>119706.4796332856</v>
       </c>
       <c r="C551" t="n">
-        <v>109597.5054103584</v>
+        <v>112977.6076419388</v>
       </c>
     </row>
     <row r="552">
@@ -6504,7 +6504,7 @@
         <v>120265.2616144133</v>
       </c>
       <c r="C552" t="n">
-        <v>110226.438894284</v>
+        <v>113517.6383438546</v>
       </c>
     </row>
     <row r="553">
@@ -6515,7 +6515,7 @@
         <v>120855.4756766929</v>
       </c>
       <c r="C553" t="n">
-        <v>110687.6670449493</v>
+        <v>114066.5034375032</v>
       </c>
     </row>
     <row r="554">
@@ -6526,7 +6526,7 @@
         <v>120970.8023761428</v>
       </c>
       <c r="C554" t="n">
-        <v>110466.5067874915</v>
+        <v>114100.562054506</v>
       </c>
     </row>
     <row r="555">
@@ -6537,7 +6537,7 @@
         <v>121668.7341462453</v>
       </c>
       <c r="C555" t="n">
-        <v>111136.122895338</v>
+        <v>114757.8817621652</v>
       </c>
     </row>
     <row r="556">
@@ -6548,7 +6548,7 @@
         <v>121506.0008541988</v>
       </c>
       <c r="C556" t="n">
-        <v>110921.4556161782</v>
+        <v>114620.0606719535</v>
       </c>
     </row>
     <row r="557">
@@ -6559,7 +6559,7 @@
         <v>120993.1993087226</v>
       </c>
       <c r="C557" t="n">
-        <v>110655.7714833975</v>
+        <v>114171.4481776056</v>
       </c>
     </row>
     <row r="558">
@@ -6570,7 +6570,7 @@
         <v>121344.1323578549</v>
       </c>
       <c r="C558" t="n">
-        <v>111201.4286894686</v>
+        <v>114531.5998502621</v>
       </c>
     </row>
     <row r="559">
@@ -6581,7 +6581,7 @@
         <v>121415.0284483837</v>
       </c>
       <c r="C559" t="n">
-        <v>111109.2164426191</v>
+        <v>114576.9624370219</v>
       </c>
     </row>
     <row r="560">
@@ -6592,7 +6592,7 @@
         <v>121008.6908533002</v>
       </c>
       <c r="C560" t="n">
-        <v>110609.0345301955</v>
+        <v>114191.1577405507</v>
       </c>
     </row>
     <row r="561">
@@ -6603,7 +6603,7 @@
         <v>121273.1067893732</v>
       </c>
       <c r="C561" t="n">
-        <v>110409.9939823481</v>
+        <v>114359.593281525</v>
       </c>
     </row>
     <row r="562">
@@ -6614,7 +6614,7 @@
         <v>121143.0227881686</v>
       </c>
       <c r="C562" t="n">
-        <v>110045.8202449278</v>
+        <v>114190.4461393208</v>
       </c>
     </row>
     <row r="563">
@@ -6625,7 +6625,7 @@
         <v>121760.8038750342</v>
       </c>
       <c r="C563" t="n">
-        <v>110026.2062024287</v>
+        <v>114716.1126508378</v>
       </c>
     </row>
     <row r="564">
@@ -6636,7 +6636,7 @@
         <v>121840.2487949436</v>
       </c>
       <c r="C564" t="n">
-        <v>110210.1928269552</v>
+        <v>114813.777016558</v>
       </c>
     </row>
     <row r="565">
@@ -6647,7 +6647,7 @@
         <v>122294.411449507</v>
       </c>
       <c r="C565" t="n">
-        <v>110610.2101772858</v>
+        <v>115250.1018316252</v>
       </c>
     </row>
     <row r="566">
@@ -6658,7 +6658,7 @@
         <v>120118.6491400161</v>
       </c>
       <c r="C566" t="n">
-        <v>108805.0731697248</v>
+        <v>113104.2937912665</v>
       </c>
     </row>
     <row r="567">
@@ -6669,7 +6669,7 @@
         <v>117758.7374161645</v>
       </c>
       <c r="C567" t="n">
-        <v>107278.5487193161</v>
+        <v>110921.8277428288</v>
       </c>
     </row>
     <row r="568">
@@ -6680,7 +6680,7 @@
         <v>116222.7684257568</v>
       </c>
       <c r="C568" t="n">
-        <v>106283.7516416809</v>
+        <v>109547.9553259199</v>
       </c>
     </row>
     <row r="569">
@@ -6691,7 +6691,7 @@
         <v>115309.8448226099</v>
       </c>
       <c r="C569" t="n">
-        <v>105287.2503404124</v>
+        <v>108562.5228209511</v>
       </c>
     </row>
     <row r="570">
@@ -6702,7 +6702,7 @@
         <v>118864.6238976772</v>
       </c>
       <c r="C570" t="n">
-        <v>108264.6305672521</v>
+        <v>111933.6805795579</v>
       </c>
     </row>
     <row r="571">
@@ -6713,7 +6713,7 @@
         <v>118032.4005234146</v>
       </c>
       <c r="C571" t="n">
-        <v>106330.9310949096</v>
+        <v>110829.3542820821</v>
       </c>
     </row>
     <row r="572">
@@ -6724,7 +6724,7 @@
         <v>119124.7283091531</v>
       </c>
       <c r="C572" t="n">
-        <v>106807.1206039299</v>
+        <v>111792.8138029217</v>
       </c>
     </row>
     <row r="573">
@@ -6735,7 +6735,7 @@
         <v>119485.9880915901</v>
       </c>
       <c r="C573" t="n">
-        <v>107561.8529749149</v>
+        <v>112208.8263306325</v>
       </c>
     </row>
     <row r="574">
@@ -6746,7 +6746,7 @@
         <v>119727.582297554</v>
       </c>
       <c r="C574" t="n">
-        <v>107746.3315221686</v>
+        <v>112392.6695099399</v>
       </c>
     </row>
     <row r="575">
@@ -6757,7 +6757,7 @@
         <v>120753.5332357204</v>
       </c>
       <c r="C575" t="n">
-        <v>107563.3255442504</v>
+        <v>113137.317301953</v>
       </c>
     </row>
     <row r="576">
@@ -6768,7 +6768,7 @@
         <v>120959.0629924423</v>
       </c>
       <c r="C576" t="n">
-        <v>107812.139676411</v>
+        <v>113414.8726470352</v>
       </c>
     </row>
     <row r="577">
@@ -6779,7 +6779,7 @@
         <v>121048.8104768518</v>
       </c>
       <c r="C577" t="n">
-        <v>106812.986773193</v>
+        <v>113139.6979747635</v>
       </c>
     </row>
     <row r="578">
@@ -6790,7 +6790,7 @@
         <v>121391.5295103743</v>
       </c>
       <c r="C578" t="n">
-        <v>107823.5214845056</v>
+        <v>113660.2171349269</v>
       </c>
     </row>
     <row r="579">
@@ -6801,7 +6801,7 @@
         <v>120942.2831379158</v>
       </c>
       <c r="C579" t="n">
-        <v>108401.7993050434</v>
+        <v>113463.5992542548</v>
       </c>
     </row>
     <row r="580">
@@ -6812,7 +6812,7 @@
         <v>122208.6721140531</v>
       </c>
       <c r="C580" t="n">
-        <v>109395.3837558423</v>
+        <v>114601.4031707317</v>
       </c>
     </row>
     <row r="581">
@@ -6823,7 +6823,7 @@
         <v>122058.1299663899</v>
       </c>
       <c r="C581" t="n">
-        <v>109612.1337905482</v>
+        <v>114573.7090386959</v>
       </c>
     </row>
     <row r="582">
@@ -6834,7 +6834,7 @@
         <v>122538.8485201889</v>
       </c>
       <c r="C582" t="n">
-        <v>109830.2307375725</v>
+        <v>114888.5069247398</v>
       </c>
     </row>
     <row r="583">
@@ -6845,7 +6845,7 @@
         <v>122226.4664320091</v>
       </c>
       <c r="C583" t="n">
-        <v>110101.726351776</v>
+        <v>114653.4240882701</v>
       </c>
     </row>
     <row r="584">
@@ -6856,7 +6856,7 @@
         <v>121434.5765824665</v>
       </c>
       <c r="C584" t="n">
-        <v>109723.3931100367</v>
+        <v>113892.2414411935</v>
       </c>
     </row>
     <row r="585">
@@ -6867,7 +6867,7 @@
         <v>120976.3421583956</v>
       </c>
       <c r="C585" t="n">
-        <v>109832.4702803823</v>
+        <v>113665.1688774688</v>
       </c>
     </row>
     <row r="586">
@@ -6878,7 +6878,7 @@
         <v>121392.3200289972</v>
       </c>
       <c r="C586" t="n">
-        <v>110248.106979846</v>
+        <v>114068.2344312068</v>
       </c>
     </row>
     <row r="587">
@@ -6889,7 +6889,7 @@
         <v>121952.0710373281</v>
       </c>
       <c r="C587" t="n">
-        <v>109941.9596101062</v>
+        <v>114301.9682203925</v>
       </c>
     </row>
     <row r="588">
@@ -6900,7 +6900,7 @@
         <v>122936.3294187868</v>
       </c>
       <c r="C588" t="n">
-        <v>109812.844358703</v>
+        <v>115031.8990536492</v>
       </c>
     </row>
     <row r="589">
@@ -6911,7 +6911,7 @@
         <v>122456.6639070254</v>
       </c>
       <c r="C589" t="n">
-        <v>110068.4615602975</v>
+        <v>114676.998339568</v>
       </c>
     </row>
     <row r="590">
@@ -6922,7 +6922,7 @@
         <v>122263.4144126497</v>
       </c>
       <c r="C590" t="n">
-        <v>110341.1606994758</v>
+        <v>114673.1542208214</v>
       </c>
     </row>
     <row r="591">
@@ -6933,7 +6933,7 @@
         <v>122615.7290092079</v>
       </c>
       <c r="C591" t="n">
-        <v>110363.895092828</v>
+        <v>114915.0762632938</v>
       </c>
     </row>
     <row r="592">
@@ -6944,7 +6944,7 @@
         <v>122632.8352469152</v>
       </c>
       <c r="C592" t="n">
-        <v>111399.5393708041</v>
+        <v>114707.3019656174</v>
       </c>
     </row>
     <row r="593">
@@ -6955,7 +6955,7 @@
         <v>123096.2961801025</v>
       </c>
       <c r="C593" t="n">
-        <v>111519.4886325099</v>
+        <v>114914.886697416</v>
       </c>
     </row>
     <row r="594">
@@ -6966,7 +6966,7 @@
         <v>122086.2850258075</v>
       </c>
       <c r="C594" t="n">
-        <v>111078.2899644579</v>
+        <v>114282.0271523193</v>
       </c>
     </row>
     <row r="595">
@@ -6977,7 +6977,7 @@
         <v>122682.4261734372</v>
       </c>
       <c r="C595" t="n">
-        <v>111509.1973940333</v>
+        <v>114773.6598624093</v>
       </c>
     </row>
     <row r="596">
@@ -6988,7 +6988,7 @@
         <v>122497.5074743442</v>
       </c>
       <c r="C596" t="n">
-        <v>111826.4509161306</v>
+        <v>114670.7689728491</v>
       </c>
     </row>
     <row r="597">
@@ -6999,7 +6999,7 @@
         <v>122765.0475463671</v>
       </c>
       <c r="C597" t="n">
-        <v>111659.3559614371</v>
+        <v>114859.9406474237</v>
       </c>
     </row>
     <row r="598">
@@ -7010,7 +7010,7 @@
         <v>123463.2357235148</v>
       </c>
       <c r="C598" t="n">
-        <v>111927.3524472831</v>
+        <v>115172.8068934091</v>
       </c>
     </row>
     <row r="599">
@@ -7021,7 +7021,7 @@
         <v>122783.1517821481</v>
       </c>
       <c r="C599" t="n">
-        <v>111460.9558529957</v>
+        <v>114718.0928744996</v>
       </c>
     </row>
     <row r="600">
@@ -7032,7 +7032,7 @@
         <v>122553.7768840194</v>
       </c>
       <c r="C600" t="n">
-        <v>111490.4807034616</v>
+        <v>114711.9802321701</v>
       </c>
     </row>
     <row r="601">
@@ -7043,7 +7043,7 @@
         <v>123285.2036333672</v>
       </c>
       <c r="C601" t="n">
-        <v>111731.5776407795</v>
+        <v>115168.0189407829</v>
       </c>
     </row>
     <row r="602">
